--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscarcuellar/ocn/media/apify_client/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35EEDF9-A5AB-6C4A-A46F-54C56012853B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2A3963-7041-724A-B3A5-6646F1844035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1560" windowWidth="19420" windowHeight="20780" xr2:uid="{52EE6F4F-3953-A140-B2A6-0482DE438E94}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="31920" windowHeight="20780" xr2:uid="{52EE6F4F-3953-A140-B2A6-0482DE438E94}"/>
   </bookViews>
   <sheets>
     <sheet name="tasks" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="61">
   <si>
     <t>task_id</t>
   </si>
@@ -138,6 +138,84 @@
   </si>
   <si>
     <t>https://www.facebook.com/poderciudadanoradio</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/ChismeOrizabaMx</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/1233543673337523/</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Balaceras Orizaba 2</t>
+  </si>
+  <si>
+    <t>Chisme Orizabeño</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/unpocodeorizabaa</t>
+  </si>
+  <si>
+    <t>GROUPS</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/386982481787894</t>
+  </si>
+  <si>
+    <t>balaceras y noticias sin censura “orizaba y zona centro de Veracruz”</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=61586769881432</t>
+  </si>
+  <si>
+    <t>Notimendez</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/ORIZABA.PROYECTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orizaba Proyectos </t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/OrizabaCapital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orizaba Capital </t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/enterateorizaba</t>
+  </si>
+  <si>
+    <t>Entérate Orizaba</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/OrizabaVer</t>
+  </si>
+  <si>
+    <t>El Vigilante Orizabeño</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/www.orizabaenred.com.mx</t>
+  </si>
+  <si>
+    <t>Orizaba en Red</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/elbuentonodecordoba</t>
+  </si>
+  <si>
+    <t>El buen tono de cordoba</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/ElMundodeOrizaba</t>
+  </si>
+  <si>
+    <t>El Mundo de Orizaba</t>
+  </si>
+  <si>
+    <t>Un Poco de Orizava</t>
   </si>
 </sst>
 </file>
@@ -1009,14 +1087,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF29DF0-388E-0142-B0F1-7C2350E3D19C}">
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="19.6640625" customWidth="1"/>
-    <col min="3" max="3" width="36.1640625" customWidth="1"/>
+    <col min="2" max="3" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="36.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1024,370 +1102,824 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>21</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>22</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>30</v>
       </c>
-      <c r="I2" t="b">
-        <v>0</v>
-      </c>
       <c r="J2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="b">
-        <v>0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>21</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>25</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>50</v>
       </c>
-      <c r="I3" t="b">
-        <v>0</v>
-      </c>
       <c r="J3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3">
         <v>15</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>30</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
       <c r="Q3" t="b">
-        <v>0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" t="b">
+        <v>0</v>
+      </c>
+      <c r="S3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>27</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>25</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>50</v>
       </c>
-      <c r="I4" t="b">
-        <v>0</v>
-      </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4">
         <v>15</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>30</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
       <c r="Q4" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>1</v>
+      </c>
+      <c r="R4" t="b">
+        <v>0</v>
+      </c>
+      <c r="S4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>21</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>25</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>30</v>
       </c>
-      <c r="I5" t="b">
-        <v>1</v>
-      </c>
       <c r="J5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="b">
-        <v>1</v>
-      </c>
-      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>15</v>
       </c>
-      <c r="P5" t="b">
-        <v>0</v>
-      </c>
       <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="R5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>31</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>25</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>30</v>
       </c>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
       <c r="J6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6">
         <v>15</v>
       </c>
-      <c r="P6" t="b">
-        <v>0</v>
-      </c>
       <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="R6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>32</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>25</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>30</v>
       </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
       <c r="J7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7">
         <v>15</v>
       </c>
-      <c r="P7" t="b">
-        <v>0</v>
-      </c>
       <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="R7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>25</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>50</v>
       </c>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
       <c r="J8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="b">
-        <v>1</v>
-      </c>
-      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8">
         <v>15</v>
       </c>
-      <c r="P8" t="b">
-        <v>0</v>
-      </c>
       <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="R8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>25</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>50</v>
       </c>
-      <c r="I9" t="b">
-        <v>1</v>
-      </c>
       <c r="J9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9">
         <v>15</v>
       </c>
-      <c r="P9" t="b">
-        <v>0</v>
-      </c>
       <c r="Q9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10">
+        <v>20</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>10</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
+      <c r="R10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11">
+        <v>20</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>10</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
+      <c r="R11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12">
+        <v>10</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>10</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13">
+        <v>5</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>10</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
+      <c r="R13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14">
+        <v>20</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>10</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15">
+        <v>30</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>20</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>0</v>
+      </c>
+      <c r="R15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16">
+        <v>50</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>20</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
+      <c r="R16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" t="s">
+        <v>58</v>
+      </c>
+      <c r="H17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17">
+        <v>25</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>15</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>0</v>
+      </c>
+      <c r="R17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H18" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18">
+        <v>35</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>15</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19">
+        <v>30</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>5</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
+      <c r="R19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" t="s">
+        <v>25</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>0</v>
+      </c>
+      <c r="R20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H21" t="s">
+        <v>25</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>0</v>
+      </c>
+      <c r="R21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>0</v>
+      </c>
+      <c r="R22" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" xr:uid="{84C75881-B9D2-E44E-8630-7B96894C43D7}"/>
-    <hyperlink ref="C9" r:id="rId2" xr:uid="{B90AFFFE-004B-9A40-B82B-C98A3D5105AF}"/>
-    <hyperlink ref="C8" r:id="rId3" xr:uid="{EC5B7B07-DA9A-E84A-8B02-2C6AF7BC807D}"/>
+    <hyperlink ref="D5" r:id="rId1" xr:uid="{84C75881-B9D2-E44E-8630-7B96894C43D7}"/>
+    <hyperlink ref="D9" r:id="rId2" xr:uid="{B90AFFFE-004B-9A40-B82B-C98A3D5105AF}"/>
+    <hyperlink ref="D8" r:id="rId3" xr:uid="{EC5B7B07-DA9A-E84A-8B02-2C6AF7BC807D}"/>
+    <hyperlink ref="D18" r:id="rId4" xr:uid="{DD330F28-7ADD-0746-A7C6-E2C6EE4C83DB}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscarcuellar/ocn/media/apify_client/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2A3963-7041-724A-B3A5-6646F1844035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A05254-A1A1-9E4D-A28E-575343F24514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="31920" windowHeight="20780" xr2:uid="{52EE6F4F-3953-A140-B2A6-0482DE438E94}"/>
   </bookViews>
@@ -215,7 +215,7 @@
     <t>El Mundo de Orizaba</t>
   </si>
   <si>
-    <t>Un Poco de Orizava</t>
+    <t>Un Poco de Orizaba</t>
   </si>
 </sst>
 </file>
@@ -1565,7 +1565,7 @@
         <v>1</v>
       </c>
       <c r="L12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12">
         <v>10</v>
@@ -1603,7 +1603,7 @@
         <v>1</v>
       </c>
       <c r="L13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13">
         <v>10</v>
@@ -1641,7 +1641,7 @@
         <v>1</v>
       </c>
       <c r="L14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14">
         <v>10</v>
@@ -1679,7 +1679,7 @@
         <v>1</v>
       </c>
       <c r="L15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15">
         <v>20</v>
@@ -1755,7 +1755,7 @@
         <v>1</v>
       </c>
       <c r="L17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17">
         <v>15</v>
@@ -1793,7 +1793,7 @@
         <v>1</v>
       </c>
       <c r="L18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18">
         <v>15</v>
@@ -1831,7 +1831,7 @@
         <v>1</v>
       </c>
       <c r="L19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19">
         <v>5</v>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -2,38 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscarcuellar/ocn/media/apify_client/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A05254-A1A1-9E4D-A28E-575343F24514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67382B7-A04C-F94F-A1B0-C689FD5FD94E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="31920" windowHeight="20780" xr2:uid="{52EE6F4F-3953-A140-B2A6-0482DE438E94}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="31920" windowHeight="20780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tasks" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="150">
   <si>
     <t>task_id</t>
   </si>
@@ -41,6 +28,9 @@
     <t>actor_class</t>
   </si>
   <si>
+    <t>name</t>
+  </si>
+  <si>
     <t>search_params</t>
   </si>
   <si>
@@ -113,6 +103,9 @@
     <t>w</t>
   </si>
   <si>
+    <t>Elimina las publicaciones que NO están relacionadas con lubricantes automotrices, aceites automotrices o mecánica automotriz. Elimina también las publicaciones cuando se pueda inferir que no se refieren a México</t>
+  </si>
+  <si>
     <t>{"keyword_search":false}</t>
   </si>
   <si>
@@ -125,9 +118,6 @@
     <t>https://www.facebook.com/DesdeElMarques</t>
   </si>
   <si>
-    <t>Elimina las publicaciones que NO están relacionadas con lubricantes automotrices, aceites automotrices o mecánica automotriz. Elimina también las publicaciones cuando se pueda inferir que no se refieren a México</t>
-  </si>
-  <si>
     <t>https://www.facebook.com/ReporteQueretaro</t>
   </si>
   <si>
@@ -140,219 +130,356 @@
     <t>https://www.facebook.com/poderciudadanoradio</t>
   </si>
   <si>
+    <t>Chisme Orizabeño</t>
+  </si>
+  <si>
     <t>https://www.facebook.com/ChismeOrizabaMx</t>
   </si>
   <si>
+    <t>Notimendez</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=61586769881432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orizaba Proyectos </t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/ORIZABA.PROYECTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orizaba Capital </t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/OrizabaCapital</t>
+  </si>
+  <si>
+    <t>El Vigilante Orizabeño</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/OrizabaVer</t>
+  </si>
+  <si>
+    <t>Orizaba en Red</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/www.orizabaenred.com.mx</t>
+  </si>
+  <si>
+    <t>El buen tono de cordoba</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/elbuentonodecordoba</t>
+  </si>
+  <si>
+    <t>El Mundo de Orizaba</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/ElMundodeOrizaba</t>
+  </si>
+  <si>
+    <t>GROUPS</t>
+  </si>
+  <si>
+    <t>Entérate Orizaba</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/enterateorizaba</t>
+  </si>
+  <si>
+    <t>Un Poco de Orizaba</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/unpocodeorizabaa</t>
+  </si>
+  <si>
+    <t>Balaceras Orizaba 2</t>
+  </si>
+  <si>
     <t>https://www.facebook.com/groups/1233543673337523/</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>Balaceras Orizaba 2</t>
-  </si>
-  <si>
-    <t>Chisme Orizabeño</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/unpocodeorizabaa</t>
-  </si>
-  <si>
-    <t>GROUPS</t>
+    <t>balaceras y noticias sin censura “orizaba y zona centro de Veracruz”</t>
   </si>
   <si>
     <t>https://www.facebook.com/groups/386982481787894</t>
   </si>
   <si>
-    <t>balaceras y noticias sin censura “orizaba y zona centro de Veracruz”</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/profile.php?id=61586769881432</t>
-  </si>
-  <si>
-    <t>Notimendez</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/ORIZABA.PROYECTOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orizaba Proyectos </t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/OrizabaCapital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orizaba Capital </t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/groups/enterateorizaba</t>
-  </si>
-  <si>
-    <t>Entérate Orizaba</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/OrizabaVer</t>
-  </si>
-  <si>
-    <t>El Vigilante Orizabeño</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/www.orizabaenred.com.mx</t>
-  </si>
-  <si>
-    <t>Orizaba en Red</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/elbuentonodecordoba</t>
-  </si>
-  <si>
-    <t>El buen tono de cordoba</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/ElMundodeOrizaba</t>
-  </si>
-  <si>
-    <t>El Mundo de Orizaba</t>
-  </si>
-  <si>
-    <t>Un Poco de Orizaba</t>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Chevron</t>
+  </si>
+  <si>
+    <t>chevron</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>BP</t>
+  </si>
+  <si>
+    <t>bp</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>British Petroleum</t>
+  </si>
+  <si>
+    <t>britishpetroleum</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>EXXON MOBIL</t>
+  </si>
+  <si>
+    <t>exxon</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Castrol</t>
+  </si>
+  <si>
+    <t>castrol</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>STP</t>
+  </si>
+  <si>
+    <t>stp</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Motul</t>
+  </si>
+  <si>
+    <t>motul</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Alioth</t>
+  </si>
+  <si>
+    <t>alioth</t>
+  </si>
+  <si>
+    <t>Mobil 1</t>
+  </si>
+  <si>
+    <t>mobil1</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>Akron</t>
+  </si>
+  <si>
+    <t>akron</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Repsol</t>
+  </si>
+  <si>
+    <t>repsol</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>Shell</t>
+  </si>
+  <si>
+    <t>shell</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Bardahl</t>
+  </si>
+  <si>
+    <t>bardahl</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>facebook_keyword_search</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>"British Petroleum"</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>"mobil 1"</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>twitter_keyword_search</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>linkedin_keyword_search</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>79</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF9C5700"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -366,188 +493,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -555,207 +509,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="43">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1086,8 +851,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF29DF0-388E-0142-B0F1-7C2350E3D19C}">
-  <dimension ref="A1:S22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="3" width="19.6640625" customWidth="1"/>
@@ -1102,55 +867,55 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
@@ -1158,19 +923,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2">
         <v>30</v>
@@ -1185,7 +950,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
@@ -1193,22 +958,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -1223,7 +988,7 @@
         <v>15</v>
       </c>
       <c r="O3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Q3" t="b">
         <v>1</v>
@@ -1232,7 +997,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
@@ -1240,22 +1005,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I4">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1270,7 +1035,7 @@
         <v>15</v>
       </c>
       <c r="O4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Q4" t="b">
         <v>1</v>
@@ -1279,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
@@ -1287,19 +1052,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I5">
         <v>30</v>
@@ -1328,13 +1093,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I6">
         <v>30</v>
@@ -1363,13 +1128,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I7">
         <v>30</v>
@@ -1398,13 +1163,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I8">
         <v>50</v>
@@ -1433,13 +1198,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I9">
         <v>50</v>
@@ -1468,16 +1233,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I10">
         <v>20</v>
@@ -1506,16 +1271,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I11">
         <v>20</v>
@@ -1544,16 +1309,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I12">
         <v>10</v>
@@ -1582,16 +1347,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I13">
         <v>5</v>
@@ -1620,16 +1385,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I14">
         <v>20</v>
@@ -1658,16 +1423,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="H15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I15">
         <v>30</v>
@@ -1696,16 +1461,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="H16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I16">
         <v>50</v>
@@ -1729,21 +1494,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I17">
         <v>25</v>
@@ -1767,21 +1532,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I18">
         <v>35</v>
@@ -1805,21 +1570,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="H19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I19">
         <v>30</v>
@@ -1843,81 +1608,2829 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="H20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>0</v>
+      </c>
+      <c r="R20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H21" t="s">
+        <v>26</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>0</v>
+      </c>
+      <c r="R21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" t="s">
         <v>25</v>
       </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="b">
-        <v>0</v>
-      </c>
-      <c r="R20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="C22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22">
+        <v>20</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>15</v>
+      </c>
+      <c r="O22" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" t="b">
+        <v>0</v>
+      </c>
+      <c r="S22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" t="s">
         <v>25</v>
       </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="b">
-        <v>0</v>
-      </c>
-      <c r="R21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="C23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23">
+        <v>20</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>15</v>
+      </c>
+      <c r="O23" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" t="b">
+        <v>0</v>
+      </c>
+      <c r="S23" t="s">
         <v>28</v>
       </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="b">
-        <v>0</v>
-      </c>
-      <c r="R22" t="b">
-        <v>1</v>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" t="s">
+        <v>70</v>
+      </c>
+      <c r="E24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24">
+        <v>20</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>15</v>
+      </c>
+      <c r="O24" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" t="b">
+        <v>0</v>
+      </c>
+      <c r="S24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" t="s">
+        <v>73</v>
+      </c>
+      <c r="E25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" t="s">
+        <v>22</v>
+      </c>
+      <c r="H25" t="s">
+        <v>26</v>
+      </c>
+      <c r="I25">
+        <v>20</v>
+      </c>
+      <c r="J25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>15</v>
+      </c>
+      <c r="O25" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" t="b">
+        <v>0</v>
+      </c>
+      <c r="S25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" t="s">
+        <v>22</v>
+      </c>
+      <c r="H26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I26">
+        <v>20</v>
+      </c>
+      <c r="J26" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>15</v>
+      </c>
+      <c r="O26" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" t="b">
+        <v>0</v>
+      </c>
+      <c r="S26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" t="s">
+        <v>22</v>
+      </c>
+      <c r="H27" t="s">
+        <v>26</v>
+      </c>
+      <c r="I27">
+        <v>20</v>
+      </c>
+      <c r="J27" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>15</v>
+      </c>
+      <c r="O27" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" t="b">
+        <v>0</v>
+      </c>
+      <c r="S27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I28">
+        <v>20</v>
+      </c>
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>15</v>
+      </c>
+      <c r="O28" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" t="b">
+        <v>0</v>
+      </c>
+      <c r="S28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" t="s">
+        <v>22</v>
+      </c>
+      <c r="H29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29">
+        <v>20</v>
+      </c>
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>15</v>
+      </c>
+      <c r="O29" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" t="b">
+        <v>0</v>
+      </c>
+      <c r="S29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" t="s">
+        <v>86</v>
+      </c>
+      <c r="D30" t="s">
+        <v>87</v>
+      </c>
+      <c r="E30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30" t="s">
+        <v>26</v>
+      </c>
+      <c r="I30">
+        <v>20</v>
+      </c>
+      <c r="J30" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>15</v>
+      </c>
+      <c r="O30" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" t="b">
+        <v>0</v>
+      </c>
+      <c r="S30" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" t="s">
+        <v>90</v>
+      </c>
+      <c r="E31" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" t="s">
+        <v>22</v>
+      </c>
+      <c r="H31" t="s">
+        <v>26</v>
+      </c>
+      <c r="I31">
+        <v>20</v>
+      </c>
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" t="b">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>15</v>
+      </c>
+      <c r="O31" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" t="b">
+        <v>0</v>
+      </c>
+      <c r="S31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32" t="s">
+        <v>21</v>
+      </c>
+      <c r="F32" t="s">
+        <v>22</v>
+      </c>
+      <c r="H32" t="s">
+        <v>26</v>
+      </c>
+      <c r="I32">
+        <v>20</v>
+      </c>
+      <c r="J32" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>15</v>
+      </c>
+      <c r="O32" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" t="b">
+        <v>0</v>
+      </c>
+      <c r="S32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" t="s">
+        <v>95</v>
+      </c>
+      <c r="D33" t="s">
+        <v>96</v>
+      </c>
+      <c r="E33" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" t="s">
+        <v>22</v>
+      </c>
+      <c r="H33" t="s">
+        <v>26</v>
+      </c>
+      <c r="I33">
+        <v>20</v>
+      </c>
+      <c r="J33" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>15</v>
+      </c>
+      <c r="O33" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="b">
+        <v>0</v>
+      </c>
+      <c r="S33" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" t="s">
+        <v>98</v>
+      </c>
+      <c r="D34" t="s">
+        <v>99</v>
+      </c>
+      <c r="E34" t="s">
+        <v>21</v>
+      </c>
+      <c r="F34" t="s">
+        <v>22</v>
+      </c>
+      <c r="H34" t="s">
+        <v>26</v>
+      </c>
+      <c r="I34">
+        <v>20</v>
+      </c>
+      <c r="J34" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>15</v>
+      </c>
+      <c r="O34" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" t="b">
+        <v>0</v>
+      </c>
+      <c r="S34" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>100</v>
+      </c>
+      <c r="B35" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" t="s">
+        <v>21</v>
+      </c>
+      <c r="F35" t="s">
+        <v>22</v>
+      </c>
+      <c r="H35" t="s">
+        <v>26</v>
+      </c>
+      <c r="I35">
+        <v>20</v>
+      </c>
+      <c r="J35" t="b">
+        <v>1</v>
+      </c>
+      <c r="K35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" t="b">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>15</v>
+      </c>
+      <c r="O35" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>0</v>
+      </c>
+      <c r="R35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" t="s">
+        <v>21</v>
+      </c>
+      <c r="F36" t="s">
+        <v>22</v>
+      </c>
+      <c r="H36" t="s">
+        <v>26</v>
+      </c>
+      <c r="I36">
+        <v>20</v>
+      </c>
+      <c r="J36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>15</v>
+      </c>
+      <c r="O36" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>103</v>
+      </c>
+      <c r="B37" t="s">
+        <v>101</v>
+      </c>
+      <c r="C37" t="s">
+        <v>62</v>
+      </c>
+      <c r="D37" t="s">
+        <v>63</v>
+      </c>
+      <c r="E37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F37" t="s">
+        <v>22</v>
+      </c>
+      <c r="H37" t="s">
+        <v>26</v>
+      </c>
+      <c r="I37">
+        <v>20</v>
+      </c>
+      <c r="J37" t="b">
+        <v>1</v>
+      </c>
+      <c r="K37" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" t="b">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>15</v>
+      </c>
+      <c r="O37" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>104</v>
+      </c>
+      <c r="B38" t="s">
+        <v>101</v>
+      </c>
+      <c r="C38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D38" t="s">
+        <v>67</v>
+      </c>
+      <c r="E38" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" t="s">
+        <v>22</v>
+      </c>
+      <c r="H38" t="s">
+        <v>26</v>
+      </c>
+      <c r="I38">
+        <v>20</v>
+      </c>
+      <c r="J38" t="b">
+        <v>1</v>
+      </c>
+      <c r="K38" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" t="b">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>15</v>
+      </c>
+      <c r="O38" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>0</v>
+      </c>
+      <c r="R38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" t="s">
+        <v>101</v>
+      </c>
+      <c r="C39" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39" t="s">
+        <v>106</v>
+      </c>
+      <c r="E39" t="s">
+        <v>21</v>
+      </c>
+      <c r="F39" t="s">
+        <v>22</v>
+      </c>
+      <c r="H39" t="s">
+        <v>26</v>
+      </c>
+      <c r="I39">
+        <v>20</v>
+      </c>
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="b">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>15</v>
+      </c>
+      <c r="O39" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>0</v>
+      </c>
+      <c r="R39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>107</v>
+      </c>
+      <c r="B40" t="s">
+        <v>101</v>
+      </c>
+      <c r="C40" t="s">
+        <v>72</v>
+      </c>
+      <c r="D40" t="s">
+        <v>73</v>
+      </c>
+      <c r="E40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F40" t="s">
+        <v>22</v>
+      </c>
+      <c r="H40" t="s">
+        <v>26</v>
+      </c>
+      <c r="I40">
+        <v>20</v>
+      </c>
+      <c r="J40" t="b">
+        <v>1</v>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" t="b">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>15</v>
+      </c>
+      <c r="O40" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>0</v>
+      </c>
+      <c r="R40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>108</v>
+      </c>
+      <c r="B41" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41" t="s">
+        <v>75</v>
+      </c>
+      <c r="D41" t="s">
+        <v>76</v>
+      </c>
+      <c r="E41" t="s">
+        <v>21</v>
+      </c>
+      <c r="F41" t="s">
+        <v>22</v>
+      </c>
+      <c r="H41" t="s">
+        <v>26</v>
+      </c>
+      <c r="I41">
+        <v>20</v>
+      </c>
+      <c r="J41" t="b">
+        <v>1</v>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" t="b">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>15</v>
+      </c>
+      <c r="O41" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>0</v>
+      </c>
+      <c r="R41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" t="s">
+        <v>101</v>
+      </c>
+      <c r="C42" t="s">
+        <v>78</v>
+      </c>
+      <c r="D42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E42" t="s">
+        <v>21</v>
+      </c>
+      <c r="F42" t="s">
+        <v>22</v>
+      </c>
+      <c r="H42" t="s">
+        <v>26</v>
+      </c>
+      <c r="I42">
+        <v>20</v>
+      </c>
+      <c r="J42" t="b">
+        <v>1</v>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" t="b">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>15</v>
+      </c>
+      <c r="O42" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q42" t="b">
+        <v>0</v>
+      </c>
+      <c r="R42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>110</v>
+      </c>
+      <c r="B43" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" t="s">
+        <v>81</v>
+      </c>
+      <c r="D43" t="s">
+        <v>82</v>
+      </c>
+      <c r="E43" t="s">
+        <v>21</v>
+      </c>
+      <c r="F43" t="s">
+        <v>22</v>
+      </c>
+      <c r="H43" t="s">
+        <v>26</v>
+      </c>
+      <c r="I43">
+        <v>20</v>
+      </c>
+      <c r="J43" t="b">
+        <v>1</v>
+      </c>
+      <c r="K43" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" t="b">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>15</v>
+      </c>
+      <c r="O43" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q43" t="b">
+        <v>0</v>
+      </c>
+      <c r="R43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>111</v>
+      </c>
+      <c r="B44" t="s">
+        <v>101</v>
+      </c>
+      <c r="C44" t="s">
+        <v>84</v>
+      </c>
+      <c r="D44" t="s">
+        <v>85</v>
+      </c>
+      <c r="E44" t="s">
+        <v>21</v>
+      </c>
+      <c r="F44" t="s">
+        <v>22</v>
+      </c>
+      <c r="H44" t="s">
+        <v>26</v>
+      </c>
+      <c r="I44">
+        <v>20</v>
+      </c>
+      <c r="J44" t="b">
+        <v>1</v>
+      </c>
+      <c r="K44" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" t="b">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>15</v>
+      </c>
+      <c r="O44" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q44" t="b">
+        <v>0</v>
+      </c>
+      <c r="R44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>112</v>
+      </c>
+      <c r="B45" t="s">
+        <v>101</v>
+      </c>
+      <c r="C45" t="s">
+        <v>86</v>
+      </c>
+      <c r="D45" t="s">
+        <v>113</v>
+      </c>
+      <c r="E45" t="s">
+        <v>21</v>
+      </c>
+      <c r="F45" t="s">
+        <v>22</v>
+      </c>
+      <c r="H45" t="s">
+        <v>26</v>
+      </c>
+      <c r="I45">
+        <v>20</v>
+      </c>
+      <c r="J45" t="b">
+        <v>1</v>
+      </c>
+      <c r="K45" t="b">
+        <v>1</v>
+      </c>
+      <c r="L45" t="b">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>15</v>
+      </c>
+      <c r="O45" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q45" t="b">
+        <v>0</v>
+      </c>
+      <c r="R45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>114</v>
+      </c>
+      <c r="B46" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" t="s">
+        <v>89</v>
+      </c>
+      <c r="D46" t="s">
+        <v>90</v>
+      </c>
+      <c r="E46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F46" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" t="s">
+        <v>26</v>
+      </c>
+      <c r="I46">
+        <v>20</v>
+      </c>
+      <c r="J46" t="b">
+        <v>1</v>
+      </c>
+      <c r="K46" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" t="b">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>15</v>
+      </c>
+      <c r="O46" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q46" t="b">
+        <v>0</v>
+      </c>
+      <c r="R46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>115</v>
+      </c>
+      <c r="B47" t="s">
+        <v>101</v>
+      </c>
+      <c r="C47" t="s">
+        <v>92</v>
+      </c>
+      <c r="D47" t="s">
+        <v>93</v>
+      </c>
+      <c r="E47" t="s">
+        <v>21</v>
+      </c>
+      <c r="F47" t="s">
+        <v>22</v>
+      </c>
+      <c r="H47" t="s">
+        <v>26</v>
+      </c>
+      <c r="I47">
+        <v>20</v>
+      </c>
+      <c r="J47" t="b">
+        <v>1</v>
+      </c>
+      <c r="K47" t="b">
+        <v>1</v>
+      </c>
+      <c r="L47" t="b">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>15</v>
+      </c>
+      <c r="O47" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q47" t="b">
+        <v>0</v>
+      </c>
+      <c r="R47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>116</v>
+      </c>
+      <c r="B48" t="s">
+        <v>101</v>
+      </c>
+      <c r="C48" t="s">
+        <v>95</v>
+      </c>
+      <c r="D48" t="s">
+        <v>96</v>
+      </c>
+      <c r="E48" t="s">
+        <v>21</v>
+      </c>
+      <c r="F48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H48" t="s">
+        <v>26</v>
+      </c>
+      <c r="I48">
+        <v>20</v>
+      </c>
+      <c r="J48" t="b">
+        <v>1</v>
+      </c>
+      <c r="K48" t="b">
+        <v>1</v>
+      </c>
+      <c r="L48" t="b">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>15</v>
+      </c>
+      <c r="O48" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q48" t="b">
+        <v>0</v>
+      </c>
+      <c r="R48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>117</v>
+      </c>
+      <c r="B49" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" t="s">
+        <v>98</v>
+      </c>
+      <c r="D49" t="s">
+        <v>99</v>
+      </c>
+      <c r="E49" t="s">
+        <v>21</v>
+      </c>
+      <c r="F49" t="s">
+        <v>22</v>
+      </c>
+      <c r="H49" t="s">
+        <v>26</v>
+      </c>
+      <c r="I49">
+        <v>20</v>
+      </c>
+      <c r="J49" t="b">
+        <v>1</v>
+      </c>
+      <c r="K49" t="b">
+        <v>1</v>
+      </c>
+      <c r="L49" t="b">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>15</v>
+      </c>
+      <c r="O49" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q49" t="b">
+        <v>0</v>
+      </c>
+      <c r="R49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>118</v>
+      </c>
+      <c r="B50" t="s">
+        <v>119</v>
+      </c>
+      <c r="C50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" t="s">
+        <v>21</v>
+      </c>
+      <c r="F50" t="s">
+        <v>22</v>
+      </c>
+      <c r="H50" t="s">
+        <v>26</v>
+      </c>
+      <c r="I50">
+        <v>20</v>
+      </c>
+      <c r="J50" t="b">
+        <v>1</v>
+      </c>
+      <c r="K50" t="b">
+        <v>1</v>
+      </c>
+      <c r="L50" t="b">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>15</v>
+      </c>
+      <c r="O50" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q50" t="b">
+        <v>0</v>
+      </c>
+      <c r="R50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>120</v>
+      </c>
+      <c r="B51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C51" t="s">
+        <v>29</v>
+      </c>
+      <c r="D51" t="s">
+        <v>29</v>
+      </c>
+      <c r="E51" t="s">
+        <v>21</v>
+      </c>
+      <c r="F51" t="s">
+        <v>22</v>
+      </c>
+      <c r="H51" t="s">
+        <v>26</v>
+      </c>
+      <c r="I51">
+        <v>20</v>
+      </c>
+      <c r="J51" t="b">
+        <v>1</v>
+      </c>
+      <c r="K51" t="b">
+        <v>1</v>
+      </c>
+      <c r="L51" t="b">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>15</v>
+      </c>
+      <c r="O51" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q51" t="b">
+        <v>0</v>
+      </c>
+      <c r="R51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>121</v>
+      </c>
+      <c r="B52" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52" t="s">
+        <v>62</v>
+      </c>
+      <c r="D52" t="s">
+        <v>63</v>
+      </c>
+      <c r="E52" t="s">
+        <v>21</v>
+      </c>
+      <c r="F52" t="s">
+        <v>22</v>
+      </c>
+      <c r="H52" t="s">
+        <v>26</v>
+      </c>
+      <c r="I52">
+        <v>20</v>
+      </c>
+      <c r="J52" t="b">
+        <v>1</v>
+      </c>
+      <c r="K52" t="b">
+        <v>1</v>
+      </c>
+      <c r="L52" t="b">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>15</v>
+      </c>
+      <c r="O52" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q52" t="b">
+        <v>0</v>
+      </c>
+      <c r="R52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>122</v>
+      </c>
+      <c r="B53" t="s">
+        <v>119</v>
+      </c>
+      <c r="C53" t="s">
+        <v>66</v>
+      </c>
+      <c r="D53" t="s">
+        <v>67</v>
+      </c>
+      <c r="E53" t="s">
+        <v>21</v>
+      </c>
+      <c r="F53" t="s">
+        <v>22</v>
+      </c>
+      <c r="H53" t="s">
+        <v>26</v>
+      </c>
+      <c r="I53">
+        <v>20</v>
+      </c>
+      <c r="J53" t="b">
+        <v>1</v>
+      </c>
+      <c r="K53" t="b">
+        <v>1</v>
+      </c>
+      <c r="L53" t="b">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>15</v>
+      </c>
+      <c r="O53" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q53" t="b">
+        <v>0</v>
+      </c>
+      <c r="R53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>123</v>
+      </c>
+      <c r="B54" t="s">
+        <v>119</v>
+      </c>
+      <c r="C54" t="s">
+        <v>69</v>
+      </c>
+      <c r="D54" t="s">
+        <v>106</v>
+      </c>
+      <c r="E54" t="s">
+        <v>21</v>
+      </c>
+      <c r="F54" t="s">
+        <v>22</v>
+      </c>
+      <c r="H54" t="s">
+        <v>26</v>
+      </c>
+      <c r="I54">
+        <v>20</v>
+      </c>
+      <c r="J54" t="b">
+        <v>1</v>
+      </c>
+      <c r="K54" t="b">
+        <v>1</v>
+      </c>
+      <c r="L54" t="b">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>15</v>
+      </c>
+      <c r="O54" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q54" t="b">
+        <v>0</v>
+      </c>
+      <c r="R54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>124</v>
+      </c>
+      <c r="B55" t="s">
+        <v>119</v>
+      </c>
+      <c r="C55" t="s">
+        <v>72</v>
+      </c>
+      <c r="D55" t="s">
+        <v>73</v>
+      </c>
+      <c r="E55" t="s">
+        <v>21</v>
+      </c>
+      <c r="F55" t="s">
+        <v>22</v>
+      </c>
+      <c r="H55" t="s">
+        <v>26</v>
+      </c>
+      <c r="I55">
+        <v>20</v>
+      </c>
+      <c r="J55" t="b">
+        <v>1</v>
+      </c>
+      <c r="K55" t="b">
+        <v>1</v>
+      </c>
+      <c r="L55" t="b">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>15</v>
+      </c>
+      <c r="O55" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q55" t="b">
+        <v>0</v>
+      </c>
+      <c r="R55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>125</v>
+      </c>
+      <c r="B56" t="s">
+        <v>119</v>
+      </c>
+      <c r="C56" t="s">
+        <v>75</v>
+      </c>
+      <c r="D56" t="s">
+        <v>76</v>
+      </c>
+      <c r="E56" t="s">
+        <v>21</v>
+      </c>
+      <c r="F56" t="s">
+        <v>22</v>
+      </c>
+      <c r="H56" t="s">
+        <v>26</v>
+      </c>
+      <c r="I56">
+        <v>20</v>
+      </c>
+      <c r="J56" t="b">
+        <v>1</v>
+      </c>
+      <c r="K56" t="b">
+        <v>1</v>
+      </c>
+      <c r="L56" t="b">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>15</v>
+      </c>
+      <c r="O56" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q56" t="b">
+        <v>0</v>
+      </c>
+      <c r="R56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" t="s">
+        <v>119</v>
+      </c>
+      <c r="C57" t="s">
+        <v>78</v>
+      </c>
+      <c r="D57" t="s">
+        <v>79</v>
+      </c>
+      <c r="E57" t="s">
+        <v>21</v>
+      </c>
+      <c r="F57" t="s">
+        <v>22</v>
+      </c>
+      <c r="H57" t="s">
+        <v>26</v>
+      </c>
+      <c r="I57">
+        <v>20</v>
+      </c>
+      <c r="J57" t="b">
+        <v>1</v>
+      </c>
+      <c r="K57" t="b">
+        <v>1</v>
+      </c>
+      <c r="L57" t="b">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>15</v>
+      </c>
+      <c r="O57" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q57" t="b">
+        <v>0</v>
+      </c>
+      <c r="R57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>127</v>
+      </c>
+      <c r="B58" t="s">
+        <v>119</v>
+      </c>
+      <c r="C58" t="s">
+        <v>81</v>
+      </c>
+      <c r="D58" t="s">
+        <v>82</v>
+      </c>
+      <c r="E58" t="s">
+        <v>21</v>
+      </c>
+      <c r="F58" t="s">
+        <v>22</v>
+      </c>
+      <c r="H58" t="s">
+        <v>26</v>
+      </c>
+      <c r="I58">
+        <v>20</v>
+      </c>
+      <c r="J58" t="b">
+        <v>1</v>
+      </c>
+      <c r="K58" t="b">
+        <v>1</v>
+      </c>
+      <c r="L58" t="b">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>15</v>
+      </c>
+      <c r="O58" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q58" t="b">
+        <v>0</v>
+      </c>
+      <c r="R58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>128</v>
+      </c>
+      <c r="B59" t="s">
+        <v>119</v>
+      </c>
+      <c r="C59" t="s">
+        <v>84</v>
+      </c>
+      <c r="D59" t="s">
+        <v>85</v>
+      </c>
+      <c r="E59" t="s">
+        <v>21</v>
+      </c>
+      <c r="F59" t="s">
+        <v>22</v>
+      </c>
+      <c r="H59" t="s">
+        <v>26</v>
+      </c>
+      <c r="I59">
+        <v>20</v>
+      </c>
+      <c r="J59" t="b">
+        <v>1</v>
+      </c>
+      <c r="K59" t="b">
+        <v>1</v>
+      </c>
+      <c r="L59" t="b">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>15</v>
+      </c>
+      <c r="O59" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q59" t="b">
+        <v>0</v>
+      </c>
+      <c r="R59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>129</v>
+      </c>
+      <c r="B60" t="s">
+        <v>119</v>
+      </c>
+      <c r="C60" t="s">
+        <v>86</v>
+      </c>
+      <c r="D60" t="s">
+        <v>113</v>
+      </c>
+      <c r="E60" t="s">
+        <v>21</v>
+      </c>
+      <c r="F60" t="s">
+        <v>22</v>
+      </c>
+      <c r="H60" t="s">
+        <v>26</v>
+      </c>
+      <c r="I60">
+        <v>20</v>
+      </c>
+      <c r="J60" t="b">
+        <v>1</v>
+      </c>
+      <c r="K60" t="b">
+        <v>1</v>
+      </c>
+      <c r="L60" t="b">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>15</v>
+      </c>
+      <c r="O60" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q60" t="b">
+        <v>0</v>
+      </c>
+      <c r="R60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>130</v>
+      </c>
+      <c r="B61" t="s">
+        <v>119</v>
+      </c>
+      <c r="C61" t="s">
+        <v>89</v>
+      </c>
+      <c r="D61" t="s">
+        <v>90</v>
+      </c>
+      <c r="E61" t="s">
+        <v>21</v>
+      </c>
+      <c r="F61" t="s">
+        <v>22</v>
+      </c>
+      <c r="H61" t="s">
+        <v>26</v>
+      </c>
+      <c r="I61">
+        <v>20</v>
+      </c>
+      <c r="J61" t="b">
+        <v>1</v>
+      </c>
+      <c r="K61" t="b">
+        <v>1</v>
+      </c>
+      <c r="L61" t="b">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>15</v>
+      </c>
+      <c r="O61" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q61" t="b">
+        <v>0</v>
+      </c>
+      <c r="R61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>131</v>
+      </c>
+      <c r="B62" t="s">
+        <v>119</v>
+      </c>
+      <c r="C62" t="s">
+        <v>92</v>
+      </c>
+      <c r="D62" t="s">
+        <v>93</v>
+      </c>
+      <c r="E62" t="s">
+        <v>21</v>
+      </c>
+      <c r="F62" t="s">
+        <v>22</v>
+      </c>
+      <c r="H62" t="s">
+        <v>26</v>
+      </c>
+      <c r="I62">
+        <v>20</v>
+      </c>
+      <c r="J62" t="b">
+        <v>1</v>
+      </c>
+      <c r="K62" t="b">
+        <v>1</v>
+      </c>
+      <c r="L62" t="b">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>15</v>
+      </c>
+      <c r="O62" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q62" t="b">
+        <v>0</v>
+      </c>
+      <c r="R62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>132</v>
+      </c>
+      <c r="B63" t="s">
+        <v>119</v>
+      </c>
+      <c r="C63" t="s">
+        <v>95</v>
+      </c>
+      <c r="D63" t="s">
+        <v>96</v>
+      </c>
+      <c r="E63" t="s">
+        <v>21</v>
+      </c>
+      <c r="F63" t="s">
+        <v>22</v>
+      </c>
+      <c r="H63" t="s">
+        <v>26</v>
+      </c>
+      <c r="I63">
+        <v>20</v>
+      </c>
+      <c r="J63" t="b">
+        <v>1</v>
+      </c>
+      <c r="K63" t="b">
+        <v>1</v>
+      </c>
+      <c r="L63" t="b">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>15</v>
+      </c>
+      <c r="O63" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q63" t="b">
+        <v>0</v>
+      </c>
+      <c r="R63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>133</v>
+      </c>
+      <c r="B64" t="s">
+        <v>119</v>
+      </c>
+      <c r="C64" t="s">
+        <v>98</v>
+      </c>
+      <c r="D64" t="s">
+        <v>99</v>
+      </c>
+      <c r="E64" t="s">
+        <v>21</v>
+      </c>
+      <c r="F64" t="s">
+        <v>22</v>
+      </c>
+      <c r="H64" t="s">
+        <v>26</v>
+      </c>
+      <c r="I64">
+        <v>20</v>
+      </c>
+      <c r="J64" t="b">
+        <v>1</v>
+      </c>
+      <c r="K64" t="b">
+        <v>1</v>
+      </c>
+      <c r="L64" t="b">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>15</v>
+      </c>
+      <c r="O64" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q64" t="b">
+        <v>0</v>
+      </c>
+      <c r="R64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>134</v>
+      </c>
+      <c r="B65" t="s">
+        <v>135</v>
+      </c>
+      <c r="C65" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65" t="s">
+        <v>20</v>
+      </c>
+      <c r="E65" t="s">
+        <v>21</v>
+      </c>
+      <c r="F65" t="s">
+        <v>22</v>
+      </c>
+      <c r="H65" t="s">
+        <v>26</v>
+      </c>
+      <c r="I65">
+        <v>20</v>
+      </c>
+      <c r="J65" t="b">
+        <v>1</v>
+      </c>
+      <c r="K65" t="b">
+        <v>1</v>
+      </c>
+      <c r="L65" t="b">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>15</v>
+      </c>
+      <c r="O65" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q65" t="b">
+        <v>0</v>
+      </c>
+      <c r="R65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>136</v>
+      </c>
+      <c r="B66" t="s">
+        <v>135</v>
+      </c>
+      <c r="C66" t="s">
+        <v>29</v>
+      </c>
+      <c r="D66" t="s">
+        <v>29</v>
+      </c>
+      <c r="E66" t="s">
+        <v>21</v>
+      </c>
+      <c r="F66" t="s">
+        <v>22</v>
+      </c>
+      <c r="H66" t="s">
+        <v>26</v>
+      </c>
+      <c r="I66">
+        <v>20</v>
+      </c>
+      <c r="J66" t="b">
+        <v>1</v>
+      </c>
+      <c r="K66" t="b">
+        <v>1</v>
+      </c>
+      <c r="L66" t="b">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>15</v>
+      </c>
+      <c r="O66" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q66" t="b">
+        <v>0</v>
+      </c>
+      <c r="R66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>137</v>
+      </c>
+      <c r="B67" t="s">
+        <v>135</v>
+      </c>
+      <c r="C67" t="s">
+        <v>62</v>
+      </c>
+      <c r="D67" t="s">
+        <v>63</v>
+      </c>
+      <c r="E67" t="s">
+        <v>21</v>
+      </c>
+      <c r="F67" t="s">
+        <v>22</v>
+      </c>
+      <c r="H67" t="s">
+        <v>26</v>
+      </c>
+      <c r="I67">
+        <v>20</v>
+      </c>
+      <c r="J67" t="b">
+        <v>1</v>
+      </c>
+      <c r="K67" t="b">
+        <v>1</v>
+      </c>
+      <c r="L67" t="b">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>15</v>
+      </c>
+      <c r="O67" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q67" t="b">
+        <v>0</v>
+      </c>
+      <c r="R67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>138</v>
+      </c>
+      <c r="B68" t="s">
+        <v>135</v>
+      </c>
+      <c r="C68" t="s">
+        <v>66</v>
+      </c>
+      <c r="D68" t="s">
+        <v>67</v>
+      </c>
+      <c r="E68" t="s">
+        <v>21</v>
+      </c>
+      <c r="F68" t="s">
+        <v>22</v>
+      </c>
+      <c r="H68" t="s">
+        <v>26</v>
+      </c>
+      <c r="I68">
+        <v>20</v>
+      </c>
+      <c r="J68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K68" t="b">
+        <v>1</v>
+      </c>
+      <c r="L68" t="b">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>15</v>
+      </c>
+      <c r="O68" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q68" t="b">
+        <v>0</v>
+      </c>
+      <c r="R68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>139</v>
+      </c>
+      <c r="B69" t="s">
+        <v>135</v>
+      </c>
+      <c r="C69" t="s">
+        <v>69</v>
+      </c>
+      <c r="D69" t="s">
+        <v>106</v>
+      </c>
+      <c r="E69" t="s">
+        <v>21</v>
+      </c>
+      <c r="F69" t="s">
+        <v>22</v>
+      </c>
+      <c r="H69" t="s">
+        <v>26</v>
+      </c>
+      <c r="I69">
+        <v>20</v>
+      </c>
+      <c r="J69" t="b">
+        <v>1</v>
+      </c>
+      <c r="K69" t="b">
+        <v>1</v>
+      </c>
+      <c r="L69" t="b">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>15</v>
+      </c>
+      <c r="O69" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q69" t="b">
+        <v>0</v>
+      </c>
+      <c r="R69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>140</v>
+      </c>
+      <c r="B70" t="s">
+        <v>135</v>
+      </c>
+      <c r="C70" t="s">
+        <v>72</v>
+      </c>
+      <c r="D70" t="s">
+        <v>73</v>
+      </c>
+      <c r="E70" t="s">
+        <v>21</v>
+      </c>
+      <c r="F70" t="s">
+        <v>22</v>
+      </c>
+      <c r="H70" t="s">
+        <v>26</v>
+      </c>
+      <c r="I70">
+        <v>20</v>
+      </c>
+      <c r="J70" t="b">
+        <v>1</v>
+      </c>
+      <c r="K70" t="b">
+        <v>1</v>
+      </c>
+      <c r="L70" t="b">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>15</v>
+      </c>
+      <c r="O70" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q70" t="b">
+        <v>0</v>
+      </c>
+      <c r="R70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>141</v>
+      </c>
+      <c r="B71" t="s">
+        <v>135</v>
+      </c>
+      <c r="C71" t="s">
+        <v>75</v>
+      </c>
+      <c r="D71" t="s">
+        <v>76</v>
+      </c>
+      <c r="E71" t="s">
+        <v>21</v>
+      </c>
+      <c r="F71" t="s">
+        <v>22</v>
+      </c>
+      <c r="H71" t="s">
+        <v>26</v>
+      </c>
+      <c r="I71">
+        <v>20</v>
+      </c>
+      <c r="J71" t="b">
+        <v>1</v>
+      </c>
+      <c r="K71" t="b">
+        <v>1</v>
+      </c>
+      <c r="L71" t="b">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>15</v>
+      </c>
+      <c r="O71" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q71" t="b">
+        <v>0</v>
+      </c>
+      <c r="R71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>142</v>
+      </c>
+      <c r="B72" t="s">
+        <v>135</v>
+      </c>
+      <c r="C72" t="s">
+        <v>78</v>
+      </c>
+      <c r="D72" t="s">
+        <v>79</v>
+      </c>
+      <c r="E72" t="s">
+        <v>21</v>
+      </c>
+      <c r="F72" t="s">
+        <v>22</v>
+      </c>
+      <c r="H72" t="s">
+        <v>26</v>
+      </c>
+      <c r="I72">
+        <v>20</v>
+      </c>
+      <c r="J72" t="b">
+        <v>1</v>
+      </c>
+      <c r="K72" t="b">
+        <v>1</v>
+      </c>
+      <c r="L72" t="b">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>15</v>
+      </c>
+      <c r="O72" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q72" t="b">
+        <v>0</v>
+      </c>
+      <c r="R72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>143</v>
+      </c>
+      <c r="B73" t="s">
+        <v>135</v>
+      </c>
+      <c r="C73" t="s">
+        <v>81</v>
+      </c>
+      <c r="D73" t="s">
+        <v>82</v>
+      </c>
+      <c r="E73" t="s">
+        <v>21</v>
+      </c>
+      <c r="F73" t="s">
+        <v>22</v>
+      </c>
+      <c r="H73" t="s">
+        <v>26</v>
+      </c>
+      <c r="I73">
+        <v>20</v>
+      </c>
+      <c r="J73" t="b">
+        <v>1</v>
+      </c>
+      <c r="K73" t="b">
+        <v>1</v>
+      </c>
+      <c r="L73" t="b">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>15</v>
+      </c>
+      <c r="O73" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q73" t="b">
+        <v>0</v>
+      </c>
+      <c r="R73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>144</v>
+      </c>
+      <c r="B74" t="s">
+        <v>135</v>
+      </c>
+      <c r="C74" t="s">
+        <v>84</v>
+      </c>
+      <c r="D74" t="s">
+        <v>85</v>
+      </c>
+      <c r="E74" t="s">
+        <v>21</v>
+      </c>
+      <c r="F74" t="s">
+        <v>22</v>
+      </c>
+      <c r="H74" t="s">
+        <v>26</v>
+      </c>
+      <c r="I74">
+        <v>20</v>
+      </c>
+      <c r="J74" t="b">
+        <v>1</v>
+      </c>
+      <c r="K74" t="b">
+        <v>1</v>
+      </c>
+      <c r="L74" t="b">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>15</v>
+      </c>
+      <c r="O74" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q74" t="b">
+        <v>0</v>
+      </c>
+      <c r="R74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>145</v>
+      </c>
+      <c r="B75" t="s">
+        <v>135</v>
+      </c>
+      <c r="C75" t="s">
+        <v>86</v>
+      </c>
+      <c r="D75" t="s">
+        <v>113</v>
+      </c>
+      <c r="E75" t="s">
+        <v>21</v>
+      </c>
+      <c r="F75" t="s">
+        <v>22</v>
+      </c>
+      <c r="H75" t="s">
+        <v>26</v>
+      </c>
+      <c r="I75">
+        <v>20</v>
+      </c>
+      <c r="J75" t="b">
+        <v>1</v>
+      </c>
+      <c r="K75" t="b">
+        <v>1</v>
+      </c>
+      <c r="L75" t="b">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>15</v>
+      </c>
+      <c r="O75" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q75" t="b">
+        <v>0</v>
+      </c>
+      <c r="R75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>146</v>
+      </c>
+      <c r="B76" t="s">
+        <v>135</v>
+      </c>
+      <c r="C76" t="s">
+        <v>89</v>
+      </c>
+      <c r="D76" t="s">
+        <v>90</v>
+      </c>
+      <c r="E76" t="s">
+        <v>21</v>
+      </c>
+      <c r="F76" t="s">
+        <v>22</v>
+      </c>
+      <c r="H76" t="s">
+        <v>26</v>
+      </c>
+      <c r="I76">
+        <v>20</v>
+      </c>
+      <c r="J76" t="b">
+        <v>1</v>
+      </c>
+      <c r="K76" t="b">
+        <v>1</v>
+      </c>
+      <c r="L76" t="b">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>15</v>
+      </c>
+      <c r="O76" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q76" t="b">
+        <v>0</v>
+      </c>
+      <c r="R76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>147</v>
+      </c>
+      <c r="B77" t="s">
+        <v>135</v>
+      </c>
+      <c r="C77" t="s">
+        <v>92</v>
+      </c>
+      <c r="D77" t="s">
+        <v>93</v>
+      </c>
+      <c r="E77" t="s">
+        <v>21</v>
+      </c>
+      <c r="F77" t="s">
+        <v>22</v>
+      </c>
+      <c r="H77" t="s">
+        <v>26</v>
+      </c>
+      <c r="I77">
+        <v>20</v>
+      </c>
+      <c r="J77" t="b">
+        <v>1</v>
+      </c>
+      <c r="K77" t="b">
+        <v>1</v>
+      </c>
+      <c r="L77" t="b">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>15</v>
+      </c>
+      <c r="O77" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q77" t="b">
+        <v>0</v>
+      </c>
+      <c r="R77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>148</v>
+      </c>
+      <c r="B78" t="s">
+        <v>135</v>
+      </c>
+      <c r="C78" t="s">
+        <v>95</v>
+      </c>
+      <c r="D78" t="s">
+        <v>96</v>
+      </c>
+      <c r="E78" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78" t="s">
+        <v>22</v>
+      </c>
+      <c r="H78" t="s">
+        <v>26</v>
+      </c>
+      <c r="I78">
+        <v>20</v>
+      </c>
+      <c r="J78" t="b">
+        <v>1</v>
+      </c>
+      <c r="K78" t="b">
+        <v>1</v>
+      </c>
+      <c r="L78" t="b">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>15</v>
+      </c>
+      <c r="O78" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q78" t="b">
+        <v>0</v>
+      </c>
+      <c r="R78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>149</v>
+      </c>
+      <c r="B79" t="s">
+        <v>135</v>
+      </c>
+      <c r="C79" t="s">
+        <v>98</v>
+      </c>
+      <c r="D79" t="s">
+        <v>99</v>
+      </c>
+      <c r="E79" t="s">
+        <v>21</v>
+      </c>
+      <c r="F79" t="s">
+        <v>22</v>
+      </c>
+      <c r="H79" t="s">
+        <v>26</v>
+      </c>
+      <c r="I79">
+        <v>20</v>
+      </c>
+      <c r="J79" t="b">
+        <v>1</v>
+      </c>
+      <c r="K79" t="b">
+        <v>1</v>
+      </c>
+      <c r="L79" t="b">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>15</v>
+      </c>
+      <c r="O79" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q79" t="b">
+        <v>0</v>
+      </c>
+      <c r="R79" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D5" r:id="rId1" xr:uid="{84C75881-B9D2-E44E-8630-7B96894C43D7}"/>
-    <hyperlink ref="D9" r:id="rId2" xr:uid="{B90AFFFE-004B-9A40-B82B-C98A3D5105AF}"/>
-    <hyperlink ref="D8" r:id="rId3" xr:uid="{EC5B7B07-DA9A-E84A-8B02-2C6AF7BC807D}"/>
-    <hyperlink ref="D18" r:id="rId4" xr:uid="{DD330F28-7ADD-0746-A7C6-E2C6EE4C83DB}"/>
+    <hyperlink ref="D5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D8" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D9" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D18" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscarcuellar/ocn/media/apify_client/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67382B7-A04C-F94F-A1B0-C689FD5FD94E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87BBECCF-3AC1-214E-814D-2C259CF5EF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="31920" windowHeight="20780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="153">
   <si>
     <t>task_id</t>
   </si>
@@ -470,6 +470,15 @@
   </si>
   <si>
     <t>79</t>
+  </si>
+  <si>
+    <t>theme</t>
+  </si>
+  <si>
+    <t>queretaro</t>
+  </si>
+  <si>
+    <t>orizaba</t>
   </si>
 </sst>
 </file>
@@ -852,14 +861,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S79"/>
+  <dimension ref="A1:T79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="3" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="36.1640625" customWidth="1"/>
+    <col min="2" max="4" width="19.6640625" customWidth="1"/>
+    <col min="5" max="5" width="36.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -867,368 +876,392 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
       <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s">
         <v>23</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>30</v>
       </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
       <c r="K2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3">
         <v>30</v>
       </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
       <c r="K3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>15</v>
-      </c>
-      <c r="O3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>15</v>
+      </c>
+      <c r="P3" t="s">
+        <v>27</v>
       </c>
       <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="s">
+        <v>1</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
         <v>29</v>
       </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
       <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4">
         <v>30</v>
       </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
       <c r="K4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>15</v>
-      </c>
-      <c r="O4" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>15</v>
+      </c>
+      <c r="P4" t="s">
+        <v>27</v>
       </c>
       <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="C5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
       <c r="F5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5">
+        <v>21</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5">
         <v>30</v>
       </c>
-      <c r="J5" t="b">
-        <v>1</v>
-      </c>
       <c r="K5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>15</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="M5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>15</v>
       </c>
       <c r="R5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>30</v>
       </c>
-      <c r="D6" t="s">
+      <c r="C6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E6" t="s">
         <v>32</v>
       </c>
-      <c r="H6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6">
+      <c r="I6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6">
         <v>30</v>
       </c>
-      <c r="J6" t="b">
-        <v>1</v>
-      </c>
       <c r="K6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>15</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="M6" t="b">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>15</v>
       </c>
       <c r="R6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
       </c>
-      <c r="D7" t="s">
+      <c r="C7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E7" t="s">
         <v>33</v>
       </c>
-      <c r="H7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7">
+      <c r="I7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7">
         <v>30</v>
       </c>
-      <c r="J7" t="b">
-        <v>1</v>
-      </c>
       <c r="K7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>15</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="M7" t="b">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>15</v>
       </c>
       <c r="R7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="C8" t="s">
+        <v>151</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8">
+      <c r="I8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8">
         <v>50</v>
       </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
       <c r="K8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8">
-        <v>15</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="M8" t="b">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>15</v>
       </c>
       <c r="R8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="C9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9">
+      <c r="I9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9">
         <v>50</v>
       </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
       <c r="K9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9">
-        <v>15</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="M9" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>15</v>
       </c>
       <c r="R9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1236,19 +1269,19 @@
         <v>30</v>
       </c>
       <c r="C10" t="s">
+        <v>152</v>
+      </c>
+      <c r="D10" t="s">
         <v>36</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>37</v>
       </c>
-      <c r="H10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10">
-        <v>20</v>
-      </c>
-      <c r="J10" t="b">
-        <v>1</v>
+      <c r="I10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10">
+        <v>20</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
@@ -1256,17 +1289,20 @@
       <c r="L10" t="b">
         <v>1</v>
       </c>
-      <c r="M10">
+      <c r="M10" t="b">
+        <v>1</v>
+      </c>
+      <c r="N10">
         <v>10</v>
       </c>
-      <c r="Q10" t="b">
-        <v>0</v>
-      </c>
       <c r="R10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1274,19 +1310,19 @@
         <v>30</v>
       </c>
       <c r="C11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" t="s">
         <v>38</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>39</v>
       </c>
-      <c r="H11" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11">
-        <v>20</v>
-      </c>
-      <c r="J11" t="b">
-        <v>1</v>
+      <c r="I11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11">
+        <v>20</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
@@ -1294,17 +1330,20 @@
       <c r="L11" t="b">
         <v>1</v>
       </c>
-      <c r="M11">
+      <c r="M11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N11">
         <v>10</v>
       </c>
-      <c r="Q11" t="b">
-        <v>0</v>
-      </c>
       <c r="R11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1312,37 +1351,40 @@
         <v>30</v>
       </c>
       <c r="C12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D12" t="s">
         <v>40</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>41</v>
       </c>
-      <c r="H12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I12">
+      <c r="I12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12">
         <v>10</v>
       </c>
-      <c r="J12" t="b">
-        <v>1</v>
-      </c>
       <c r="K12" t="b">
         <v>1</v>
       </c>
       <c r="L12" t="b">
-        <v>0</v>
-      </c>
-      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="M12" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12">
         <v>10</v>
       </c>
-      <c r="Q12" t="b">
-        <v>0</v>
-      </c>
       <c r="R12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1350,37 +1392,40 @@
         <v>30</v>
       </c>
       <c r="C13" t="s">
+        <v>152</v>
+      </c>
+      <c r="D13" t="s">
         <v>42</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>43</v>
       </c>
-      <c r="H13" t="s">
-        <v>26</v>
-      </c>
-      <c r="I13">
+      <c r="I13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13">
         <v>5</v>
       </c>
-      <c r="J13" t="b">
-        <v>1</v>
-      </c>
       <c r="K13" t="b">
         <v>1</v>
       </c>
       <c r="L13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="M13" t="b">
+        <v>0</v>
+      </c>
+      <c r="N13">
         <v>10</v>
       </c>
-      <c r="Q13" t="b">
-        <v>0</v>
-      </c>
       <c r="R13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1388,37 +1433,40 @@
         <v>30</v>
       </c>
       <c r="C14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D14" t="s">
         <v>44</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>45</v>
       </c>
-      <c r="H14" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14">
-        <v>20</v>
-      </c>
-      <c r="J14" t="b">
-        <v>1</v>
+      <c r="I14" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14">
+        <v>20</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
       </c>
       <c r="L14" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="M14" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14">
         <v>10</v>
       </c>
-      <c r="Q14" t="b">
-        <v>0</v>
-      </c>
       <c r="R14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1426,37 +1474,40 @@
         <v>30</v>
       </c>
       <c r="C15" t="s">
+        <v>152</v>
+      </c>
+      <c r="D15" t="s">
         <v>46</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>47</v>
       </c>
-      <c r="H15" t="s">
-        <v>26</v>
-      </c>
-      <c r="I15">
+      <c r="I15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15">
         <v>30</v>
       </c>
-      <c r="J15" t="b">
-        <v>1</v>
-      </c>
       <c r="K15" t="b">
         <v>1</v>
       </c>
       <c r="L15" t="b">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>20</v>
-      </c>
-      <c r="Q15" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M15" t="b">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>20</v>
       </c>
       <c r="R15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1464,37 +1515,40 @@
         <v>30</v>
       </c>
       <c r="C16" t="s">
+        <v>152</v>
+      </c>
+      <c r="D16" t="s">
         <v>48</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>49</v>
       </c>
-      <c r="H16" t="s">
-        <v>26</v>
-      </c>
-      <c r="I16">
+      <c r="I16" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16">
         <v>50</v>
       </c>
-      <c r="J16" t="b">
-        <v>1</v>
-      </c>
       <c r="K16" t="b">
         <v>1</v>
       </c>
       <c r="L16" t="b">
         <v>1</v>
       </c>
-      <c r="M16">
-        <v>20</v>
-      </c>
-      <c r="Q16" t="b">
-        <v>0</v>
+      <c r="M16" t="b">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>20</v>
       </c>
       <c r="R16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1502,37 +1556,40 @@
         <v>30</v>
       </c>
       <c r="C17" t="s">
+        <v>152</v>
+      </c>
+      <c r="D17" t="s">
         <v>50</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>51</v>
       </c>
-      <c r="H17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I17">
+      <c r="I17" t="s">
+        <v>26</v>
+      </c>
+      <c r="J17">
         <v>25</v>
       </c>
-      <c r="J17" t="b">
-        <v>1</v>
-      </c>
       <c r="K17" t="b">
         <v>1</v>
       </c>
       <c r="L17" t="b">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>15</v>
-      </c>
-      <c r="Q17" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M17" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>15</v>
       </c>
       <c r="R17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1540,37 +1597,40 @@
         <v>52</v>
       </c>
       <c r="C18" t="s">
+        <v>152</v>
+      </c>
+      <c r="D18" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="H18" t="s">
-        <v>26</v>
-      </c>
-      <c r="I18">
+      <c r="I18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18">
         <v>35</v>
       </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
       <c r="K18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>15</v>
-      </c>
-      <c r="Q18" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M18" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>15</v>
       </c>
       <c r="R18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1578,37 +1638,40 @@
         <v>30</v>
       </c>
       <c r="C19" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" t="s">
         <v>55</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>56</v>
       </c>
-      <c r="H19" t="s">
-        <v>26</v>
-      </c>
-      <c r="I19">
+      <c r="I19" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19">
         <v>30</v>
       </c>
-      <c r="J19" t="b">
-        <v>1</v>
-      </c>
       <c r="K19" t="b">
         <v>1</v>
       </c>
       <c r="L19" t="b">
-        <v>0</v>
-      </c>
-      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="M19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19">
         <v>5</v>
       </c>
-      <c r="Q19" t="b">
-        <v>0</v>
-      </c>
       <c r="R19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1616,25 +1679,28 @@
         <v>52</v>
       </c>
       <c r="C20" t="s">
+        <v>152</v>
+      </c>
+      <c r="D20" t="s">
         <v>57</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>58</v>
       </c>
-      <c r="H20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="b">
+      <c r="I20" t="s">
+        <v>26</v>
+      </c>
+      <c r="K20" t="b">
         <v>0</v>
       </c>
       <c r="R20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1642,25 +1708,28 @@
         <v>52</v>
       </c>
       <c r="C21" t="s">
+        <v>152</v>
+      </c>
+      <c r="D21" t="s">
         <v>59</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>60</v>
       </c>
-      <c r="H21" t="s">
-        <v>26</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="b">
+      <c r="I21" t="s">
+        <v>26</v>
+      </c>
+      <c r="K21" t="b">
         <v>0</v>
       </c>
       <c r="R21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>61</v>
       </c>
@@ -1668,49 +1737,52 @@
         <v>25</v>
       </c>
       <c r="C22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
         <v>62</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>63</v>
       </c>
-      <c r="E22" t="s">
-        <v>21</v>
-      </c>
       <c r="F22" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" t="s">
-        <v>26</v>
-      </c>
-      <c r="I22">
-        <v>20</v>
-      </c>
-      <c r="J22" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G22" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22">
+        <v>20</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
       </c>
       <c r="L22" t="b">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>15</v>
-      </c>
-      <c r="O22" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q22" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>15</v>
+      </c>
+      <c r="P22" t="s">
+        <v>27</v>
       </c>
       <c r="R22" t="b">
-        <v>0</v>
-      </c>
-      <c r="S22" t="s">
+        <v>1</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>65</v>
       </c>
@@ -1718,49 +1790,52 @@
         <v>25</v>
       </c>
       <c r="C23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" t="s">
         <v>66</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>67</v>
       </c>
-      <c r="E23" t="s">
-        <v>21</v>
-      </c>
       <c r="F23" t="s">
-        <v>22</v>
-      </c>
-      <c r="H23" t="s">
-        <v>26</v>
-      </c>
-      <c r="I23">
-        <v>20</v>
-      </c>
-      <c r="J23" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G23" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J23">
+        <v>20</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
       </c>
       <c r="L23" t="b">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>15</v>
-      </c>
-      <c r="O23" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q23" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M23" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>15</v>
+      </c>
+      <c r="P23" t="s">
+        <v>27</v>
       </c>
       <c r="R23" t="b">
-        <v>0</v>
-      </c>
-      <c r="S23" t="s">
+        <v>1</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>68</v>
       </c>
@@ -1768,49 +1843,52 @@
         <v>25</v>
       </c>
       <c r="C24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" t="s">
         <v>69</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>70</v>
       </c>
-      <c r="E24" t="s">
-        <v>21</v>
-      </c>
       <c r="F24" t="s">
-        <v>22</v>
-      </c>
-      <c r="H24" t="s">
-        <v>26</v>
-      </c>
-      <c r="I24">
-        <v>20</v>
-      </c>
-      <c r="J24" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G24" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" t="s">
+        <v>26</v>
+      </c>
+      <c r="J24">
+        <v>20</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
       </c>
       <c r="L24" t="b">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>15</v>
-      </c>
-      <c r="O24" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q24" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M24" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>15</v>
+      </c>
+      <c r="P24" t="s">
+        <v>27</v>
       </c>
       <c r="R24" t="b">
-        <v>0</v>
-      </c>
-      <c r="S24" t="s">
+        <v>1</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -1818,49 +1896,52 @@
         <v>25</v>
       </c>
       <c r="C25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" t="s">
         <v>72</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>73</v>
       </c>
-      <c r="E25" t="s">
-        <v>21</v>
-      </c>
       <c r="F25" t="s">
-        <v>22</v>
-      </c>
-      <c r="H25" t="s">
-        <v>26</v>
-      </c>
-      <c r="I25">
-        <v>20</v>
-      </c>
-      <c r="J25" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G25" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J25">
+        <v>20</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
       </c>
       <c r="L25" t="b">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>15</v>
-      </c>
-      <c r="O25" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q25" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M25" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>15</v>
+      </c>
+      <c r="P25" t="s">
+        <v>27</v>
       </c>
       <c r="R25" t="b">
-        <v>0</v>
-      </c>
-      <c r="S25" t="s">
+        <v>1</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>74</v>
       </c>
@@ -1868,49 +1949,52 @@
         <v>25</v>
       </c>
       <c r="C26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" t="s">
         <v>75</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>76</v>
       </c>
-      <c r="E26" t="s">
-        <v>21</v>
-      </c>
       <c r="F26" t="s">
-        <v>22</v>
-      </c>
-      <c r="H26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I26">
-        <v>20</v>
-      </c>
-      <c r="J26" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G26" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J26">
+        <v>20</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
       </c>
       <c r="L26" t="b">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>15</v>
-      </c>
-      <c r="O26" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q26" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M26" t="b">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>15</v>
+      </c>
+      <c r="P26" t="s">
+        <v>27</v>
       </c>
       <c r="R26" t="b">
-        <v>0</v>
-      </c>
-      <c r="S26" t="s">
+        <v>1</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>77</v>
       </c>
@@ -1918,49 +2002,52 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" t="s">
         <v>78</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>79</v>
       </c>
-      <c r="E27" t="s">
-        <v>21</v>
-      </c>
       <c r="F27" t="s">
-        <v>22</v>
-      </c>
-      <c r="H27" t="s">
-        <v>26</v>
-      </c>
-      <c r="I27">
-        <v>20</v>
-      </c>
-      <c r="J27" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G27" t="s">
+        <v>22</v>
+      </c>
+      <c r="I27" t="s">
+        <v>26</v>
+      </c>
+      <c r="J27">
+        <v>20</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
       </c>
       <c r="L27" t="b">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>15</v>
-      </c>
-      <c r="O27" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q27" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M27" t="b">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>15</v>
+      </c>
+      <c r="P27" t="s">
+        <v>27</v>
       </c>
       <c r="R27" t="b">
-        <v>0</v>
-      </c>
-      <c r="S27" t="s">
+        <v>1</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>80</v>
       </c>
@@ -1968,49 +2055,52 @@
         <v>25</v>
       </c>
       <c r="C28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" t="s">
         <v>81</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>82</v>
       </c>
-      <c r="E28" t="s">
-        <v>21</v>
-      </c>
       <c r="F28" t="s">
-        <v>22</v>
-      </c>
-      <c r="H28" t="s">
-        <v>26</v>
-      </c>
-      <c r="I28">
-        <v>20</v>
-      </c>
-      <c r="J28" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J28">
+        <v>20</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
       </c>
       <c r="L28" t="b">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>15</v>
-      </c>
-      <c r="O28" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q28" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M28" t="b">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>15</v>
+      </c>
+      <c r="P28" t="s">
+        <v>27</v>
       </c>
       <c r="R28" t="b">
-        <v>0</v>
-      </c>
-      <c r="S28" t="s">
+        <v>1</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>83</v>
       </c>
@@ -2018,49 +2108,52 @@
         <v>25</v>
       </c>
       <c r="C29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" t="s">
         <v>84</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>85</v>
       </c>
-      <c r="E29" t="s">
-        <v>21</v>
-      </c>
       <c r="F29" t="s">
-        <v>22</v>
-      </c>
-      <c r="H29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I29">
-        <v>20</v>
-      </c>
-      <c r="J29" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G29" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" t="s">
+        <v>26</v>
+      </c>
+      <c r="J29">
+        <v>20</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
       </c>
       <c r="L29" t="b">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>15</v>
-      </c>
-      <c r="O29" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q29" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M29" t="b">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>15</v>
+      </c>
+      <c r="P29" t="s">
+        <v>27</v>
       </c>
       <c r="R29" t="b">
-        <v>0</v>
-      </c>
-      <c r="S29" t="s">
+        <v>1</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>64</v>
       </c>
@@ -2068,49 +2161,52 @@
         <v>25</v>
       </c>
       <c r="C30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" t="s">
         <v>86</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>87</v>
       </c>
-      <c r="E30" t="s">
-        <v>21</v>
-      </c>
       <c r="F30" t="s">
-        <v>22</v>
-      </c>
-      <c r="H30" t="s">
-        <v>26</v>
-      </c>
-      <c r="I30">
-        <v>20</v>
-      </c>
-      <c r="J30" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G30" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" t="s">
+        <v>26</v>
+      </c>
+      <c r="J30">
+        <v>20</v>
       </c>
       <c r="K30" t="b">
         <v>1</v>
       </c>
       <c r="L30" t="b">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>15</v>
-      </c>
-      <c r="O30" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q30" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>15</v>
+      </c>
+      <c r="P30" t="s">
+        <v>27</v>
       </c>
       <c r="R30" t="b">
-        <v>0</v>
-      </c>
-      <c r="S30" t="s">
+        <v>1</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>88</v>
       </c>
@@ -2118,49 +2214,52 @@
         <v>25</v>
       </c>
       <c r="C31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" t="s">
         <v>89</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>90</v>
       </c>
-      <c r="E31" t="s">
-        <v>21</v>
-      </c>
       <c r="F31" t="s">
-        <v>22</v>
-      </c>
-      <c r="H31" t="s">
-        <v>26</v>
-      </c>
-      <c r="I31">
-        <v>20</v>
-      </c>
-      <c r="J31" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I31" t="s">
+        <v>26</v>
+      </c>
+      <c r="J31">
+        <v>20</v>
       </c>
       <c r="K31" t="b">
         <v>1</v>
       </c>
       <c r="L31" t="b">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>15</v>
-      </c>
-      <c r="O31" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q31" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M31" t="b">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>15</v>
+      </c>
+      <c r="P31" t="s">
+        <v>27</v>
       </c>
       <c r="R31" t="b">
-        <v>0</v>
-      </c>
-      <c r="S31" t="s">
+        <v>1</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>91</v>
       </c>
@@ -2168,49 +2267,52 @@
         <v>25</v>
       </c>
       <c r="C32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" t="s">
         <v>92</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>93</v>
       </c>
-      <c r="E32" t="s">
-        <v>21</v>
-      </c>
       <c r="F32" t="s">
-        <v>22</v>
-      </c>
-      <c r="H32" t="s">
-        <v>26</v>
-      </c>
-      <c r="I32">
-        <v>20</v>
-      </c>
-      <c r="J32" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G32" t="s">
+        <v>22</v>
+      </c>
+      <c r="I32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J32">
+        <v>20</v>
       </c>
       <c r="K32" t="b">
         <v>1</v>
       </c>
       <c r="L32" t="b">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>15</v>
-      </c>
-      <c r="O32" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q32" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M32" t="b">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>15</v>
+      </c>
+      <c r="P32" t="s">
+        <v>27</v>
       </c>
       <c r="R32" t="b">
-        <v>0</v>
-      </c>
-      <c r="S32" t="s">
+        <v>1</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>94</v>
       </c>
@@ -2218,49 +2320,52 @@
         <v>25</v>
       </c>
       <c r="C33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" t="s">
         <v>95</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>96</v>
       </c>
-      <c r="E33" t="s">
-        <v>21</v>
-      </c>
       <c r="F33" t="s">
-        <v>22</v>
-      </c>
-      <c r="H33" t="s">
-        <v>26</v>
-      </c>
-      <c r="I33">
-        <v>20</v>
-      </c>
-      <c r="J33" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I33" t="s">
+        <v>26</v>
+      </c>
+      <c r="J33">
+        <v>20</v>
       </c>
       <c r="K33" t="b">
         <v>1</v>
       </c>
       <c r="L33" t="b">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>15</v>
-      </c>
-      <c r="O33" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q33" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>15</v>
+      </c>
+      <c r="P33" t="s">
+        <v>27</v>
       </c>
       <c r="R33" t="b">
-        <v>0</v>
-      </c>
-      <c r="S33" t="s">
+        <v>1</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>97</v>
       </c>
@@ -2268,49 +2373,52 @@
         <v>25</v>
       </c>
       <c r="C34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" t="s">
         <v>98</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>99</v>
       </c>
-      <c r="E34" t="s">
-        <v>21</v>
-      </c>
       <c r="F34" t="s">
-        <v>22</v>
-      </c>
-      <c r="H34" t="s">
-        <v>26</v>
-      </c>
-      <c r="I34">
-        <v>20</v>
-      </c>
-      <c r="J34" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G34" t="s">
+        <v>22</v>
+      </c>
+      <c r="I34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J34">
+        <v>20</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
       </c>
       <c r="L34" t="b">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>15</v>
-      </c>
-      <c r="O34" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q34" t="b">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>15</v>
+      </c>
+      <c r="P34" t="s">
+        <v>27</v>
       </c>
       <c r="R34" t="b">
-        <v>0</v>
-      </c>
-      <c r="S34" t="s">
+        <v>1</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>100</v>
       </c>
@@ -2324,40 +2432,43 @@
         <v>20</v>
       </c>
       <c r="E35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F35" t="s">
-        <v>22</v>
-      </c>
-      <c r="H35" t="s">
-        <v>26</v>
-      </c>
-      <c r="I35">
-        <v>20</v>
-      </c>
-      <c r="J35" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G35" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" t="s">
+        <v>26</v>
+      </c>
+      <c r="J35">
+        <v>20</v>
       </c>
       <c r="K35" t="b">
         <v>1</v>
       </c>
       <c r="L35" t="b">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>15</v>
-      </c>
-      <c r="O35" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q35" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M35" t="b">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>15</v>
+      </c>
+      <c r="P35" t="s">
+        <v>27</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>102</v>
       </c>
@@ -2365,46 +2476,49 @@
         <v>101</v>
       </c>
       <c r="C36" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D36" t="s">
         <v>29</v>
       </c>
       <c r="E36" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F36" t="s">
-        <v>22</v>
-      </c>
-      <c r="H36" t="s">
-        <v>26</v>
-      </c>
-      <c r="I36">
-        <v>20</v>
-      </c>
-      <c r="J36" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G36" t="s">
+        <v>22</v>
+      </c>
+      <c r="I36" t="s">
+        <v>26</v>
+      </c>
+      <c r="J36">
+        <v>20</v>
       </c>
       <c r="K36" t="b">
         <v>1</v>
       </c>
       <c r="L36" t="b">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>15</v>
-      </c>
-      <c r="O36" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q36" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M36" t="b">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>15</v>
+      </c>
+      <c r="P36" t="s">
+        <v>27</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>103</v>
       </c>
@@ -2412,46 +2526,49 @@
         <v>101</v>
       </c>
       <c r="C37" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" t="s">
         <v>62</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>63</v>
       </c>
-      <c r="E37" t="s">
-        <v>21</v>
-      </c>
       <c r="F37" t="s">
-        <v>22</v>
-      </c>
-      <c r="H37" t="s">
-        <v>26</v>
-      </c>
-      <c r="I37">
-        <v>20</v>
-      </c>
-      <c r="J37" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G37" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" t="s">
+        <v>26</v>
+      </c>
+      <c r="J37">
+        <v>20</v>
       </c>
       <c r="K37" t="b">
         <v>1</v>
       </c>
       <c r="L37" t="b">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>15</v>
-      </c>
-      <c r="O37" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q37" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M37" t="b">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>15</v>
+      </c>
+      <c r="P37" t="s">
+        <v>27</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>104</v>
       </c>
@@ -2459,46 +2576,49 @@
         <v>101</v>
       </c>
       <c r="C38" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" t="s">
         <v>66</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>67</v>
       </c>
-      <c r="E38" t="s">
-        <v>21</v>
-      </c>
       <c r="F38" t="s">
-        <v>22</v>
-      </c>
-      <c r="H38" t="s">
-        <v>26</v>
-      </c>
-      <c r="I38">
-        <v>20</v>
-      </c>
-      <c r="J38" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G38" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" t="s">
+        <v>26</v>
+      </c>
+      <c r="J38">
+        <v>20</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
       </c>
       <c r="L38" t="b">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <v>15</v>
-      </c>
-      <c r="O38" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q38" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M38" t="b">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>15</v>
+      </c>
+      <c r="P38" t="s">
+        <v>27</v>
       </c>
       <c r="R38" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>105</v>
       </c>
@@ -2506,46 +2626,49 @@
         <v>101</v>
       </c>
       <c r="C39" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" t="s">
         <v>69</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>106</v>
       </c>
-      <c r="E39" t="s">
-        <v>21</v>
-      </c>
       <c r="F39" t="s">
-        <v>22</v>
-      </c>
-      <c r="H39" t="s">
-        <v>26</v>
-      </c>
-      <c r="I39">
-        <v>20</v>
-      </c>
-      <c r="J39" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G39" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" t="s">
+        <v>26</v>
+      </c>
+      <c r="J39">
+        <v>20</v>
       </c>
       <c r="K39" t="b">
         <v>1</v>
       </c>
       <c r="L39" t="b">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <v>15</v>
-      </c>
-      <c r="O39" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q39" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M39" t="b">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>15</v>
+      </c>
+      <c r="P39" t="s">
+        <v>27</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>107</v>
       </c>
@@ -2553,46 +2676,49 @@
         <v>101</v>
       </c>
       <c r="C40" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" t="s">
         <v>72</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>73</v>
       </c>
-      <c r="E40" t="s">
-        <v>21</v>
-      </c>
       <c r="F40" t="s">
-        <v>22</v>
-      </c>
-      <c r="H40" t="s">
-        <v>26</v>
-      </c>
-      <c r="I40">
-        <v>20</v>
-      </c>
-      <c r="J40" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G40" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" t="s">
+        <v>26</v>
+      </c>
+      <c r="J40">
+        <v>20</v>
       </c>
       <c r="K40" t="b">
         <v>1</v>
       </c>
       <c r="L40" t="b">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>15</v>
-      </c>
-      <c r="O40" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q40" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M40" t="b">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>15</v>
+      </c>
+      <c r="P40" t="s">
+        <v>27</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>108</v>
       </c>
@@ -2600,46 +2726,49 @@
         <v>101</v>
       </c>
       <c r="C41" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" t="s">
         <v>75</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>76</v>
       </c>
-      <c r="E41" t="s">
-        <v>21</v>
-      </c>
       <c r="F41" t="s">
-        <v>22</v>
-      </c>
-      <c r="H41" t="s">
-        <v>26</v>
-      </c>
-      <c r="I41">
-        <v>20</v>
-      </c>
-      <c r="J41" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G41" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" t="s">
+        <v>26</v>
+      </c>
+      <c r="J41">
+        <v>20</v>
       </c>
       <c r="K41" t="b">
         <v>1</v>
       </c>
       <c r="L41" t="b">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>15</v>
-      </c>
-      <c r="O41" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q41" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M41" t="b">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>15</v>
+      </c>
+      <c r="P41" t="s">
+        <v>27</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>109</v>
       </c>
@@ -2647,46 +2776,49 @@
         <v>101</v>
       </c>
       <c r="C42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" t="s">
         <v>78</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>79</v>
       </c>
-      <c r="E42" t="s">
-        <v>21</v>
-      </c>
       <c r="F42" t="s">
-        <v>22</v>
-      </c>
-      <c r="H42" t="s">
-        <v>26</v>
-      </c>
-      <c r="I42">
-        <v>20</v>
-      </c>
-      <c r="J42" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G42" t="s">
+        <v>22</v>
+      </c>
+      <c r="I42" t="s">
+        <v>26</v>
+      </c>
+      <c r="J42">
+        <v>20</v>
       </c>
       <c r="K42" t="b">
         <v>1</v>
       </c>
       <c r="L42" t="b">
-        <v>0</v>
-      </c>
-      <c r="M42">
-        <v>15</v>
-      </c>
-      <c r="O42" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q42" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M42" t="b">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>15</v>
+      </c>
+      <c r="P42" t="s">
+        <v>27</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>110</v>
       </c>
@@ -2694,46 +2826,49 @@
         <v>101</v>
       </c>
       <c r="C43" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" t="s">
         <v>81</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>82</v>
       </c>
-      <c r="E43" t="s">
-        <v>21</v>
-      </c>
       <c r="F43" t="s">
-        <v>22</v>
-      </c>
-      <c r="H43" t="s">
-        <v>26</v>
-      </c>
-      <c r="I43">
-        <v>20</v>
-      </c>
-      <c r="J43" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G43" t="s">
+        <v>22</v>
+      </c>
+      <c r="I43" t="s">
+        <v>26</v>
+      </c>
+      <c r="J43">
+        <v>20</v>
       </c>
       <c r="K43" t="b">
         <v>1</v>
       </c>
       <c r="L43" t="b">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>15</v>
-      </c>
-      <c r="O43" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q43" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M43" t="b">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>15</v>
+      </c>
+      <c r="P43" t="s">
+        <v>27</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>111</v>
       </c>
@@ -2741,46 +2876,49 @@
         <v>101</v>
       </c>
       <c r="C44" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" t="s">
         <v>84</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>85</v>
       </c>
-      <c r="E44" t="s">
-        <v>21</v>
-      </c>
       <c r="F44" t="s">
-        <v>22</v>
-      </c>
-      <c r="H44" t="s">
-        <v>26</v>
-      </c>
-      <c r="I44">
-        <v>20</v>
-      </c>
-      <c r="J44" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G44" t="s">
+        <v>22</v>
+      </c>
+      <c r="I44" t="s">
+        <v>26</v>
+      </c>
+      <c r="J44">
+        <v>20</v>
       </c>
       <c r="K44" t="b">
         <v>1</v>
       </c>
       <c r="L44" t="b">
-        <v>0</v>
-      </c>
-      <c r="M44">
-        <v>15</v>
-      </c>
-      <c r="O44" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q44" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M44" t="b">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>15</v>
+      </c>
+      <c r="P44" t="s">
+        <v>27</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>112</v>
       </c>
@@ -2788,46 +2926,49 @@
         <v>101</v>
       </c>
       <c r="C45" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" t="s">
         <v>86</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>113</v>
       </c>
-      <c r="E45" t="s">
-        <v>21</v>
-      </c>
       <c r="F45" t="s">
-        <v>22</v>
-      </c>
-      <c r="H45" t="s">
-        <v>26</v>
-      </c>
-      <c r="I45">
-        <v>20</v>
-      </c>
-      <c r="J45" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G45" t="s">
+        <v>22</v>
+      </c>
+      <c r="I45" t="s">
+        <v>26</v>
+      </c>
+      <c r="J45">
+        <v>20</v>
       </c>
       <c r="K45" t="b">
         <v>1</v>
       </c>
       <c r="L45" t="b">
-        <v>0</v>
-      </c>
-      <c r="M45">
-        <v>15</v>
-      </c>
-      <c r="O45" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q45" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M45" t="b">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>15</v>
+      </c>
+      <c r="P45" t="s">
+        <v>27</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>114</v>
       </c>
@@ -2835,46 +2976,49 @@
         <v>101</v>
       </c>
       <c r="C46" t="s">
+        <v>20</v>
+      </c>
+      <c r="D46" t="s">
         <v>89</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>90</v>
       </c>
-      <c r="E46" t="s">
-        <v>21</v>
-      </c>
       <c r="F46" t="s">
-        <v>22</v>
-      </c>
-      <c r="H46" t="s">
-        <v>26</v>
-      </c>
-      <c r="I46">
-        <v>20</v>
-      </c>
-      <c r="J46" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G46" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" t="s">
+        <v>26</v>
+      </c>
+      <c r="J46">
+        <v>20</v>
       </c>
       <c r="K46" t="b">
         <v>1</v>
       </c>
       <c r="L46" t="b">
-        <v>0</v>
-      </c>
-      <c r="M46">
-        <v>15</v>
-      </c>
-      <c r="O46" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q46" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M46" t="b">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>15</v>
+      </c>
+      <c r="P46" t="s">
+        <v>27</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>115</v>
       </c>
@@ -2882,46 +3026,49 @@
         <v>101</v>
       </c>
       <c r="C47" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" t="s">
         <v>92</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>93</v>
       </c>
-      <c r="E47" t="s">
-        <v>21</v>
-      </c>
       <c r="F47" t="s">
-        <v>22</v>
-      </c>
-      <c r="H47" t="s">
-        <v>26</v>
-      </c>
-      <c r="I47">
-        <v>20</v>
-      </c>
-      <c r="J47" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G47" t="s">
+        <v>22</v>
+      </c>
+      <c r="I47" t="s">
+        <v>26</v>
+      </c>
+      <c r="J47">
+        <v>20</v>
       </c>
       <c r="K47" t="b">
         <v>1</v>
       </c>
       <c r="L47" t="b">
-        <v>0</v>
-      </c>
-      <c r="M47">
-        <v>15</v>
-      </c>
-      <c r="O47" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q47" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M47" t="b">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>15</v>
+      </c>
+      <c r="P47" t="s">
+        <v>27</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>116</v>
       </c>
@@ -2929,46 +3076,49 @@
         <v>101</v>
       </c>
       <c r="C48" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48" t="s">
         <v>95</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>96</v>
       </c>
-      <c r="E48" t="s">
-        <v>21</v>
-      </c>
       <c r="F48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H48" t="s">
-        <v>26</v>
-      </c>
-      <c r="I48">
-        <v>20</v>
-      </c>
-      <c r="J48" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I48" t="s">
+        <v>26</v>
+      </c>
+      <c r="J48">
+        <v>20</v>
       </c>
       <c r="K48" t="b">
         <v>1</v>
       </c>
       <c r="L48" t="b">
-        <v>0</v>
-      </c>
-      <c r="M48">
-        <v>15</v>
-      </c>
-      <c r="O48" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q48" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M48" t="b">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>15</v>
+      </c>
+      <c r="P48" t="s">
+        <v>27</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>117</v>
       </c>
@@ -2976,46 +3126,49 @@
         <v>101</v>
       </c>
       <c r="C49" t="s">
+        <v>20</v>
+      </c>
+      <c r="D49" t="s">
         <v>98</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>99</v>
       </c>
-      <c r="E49" t="s">
-        <v>21</v>
-      </c>
       <c r="F49" t="s">
-        <v>22</v>
-      </c>
-      <c r="H49" t="s">
-        <v>26</v>
-      </c>
-      <c r="I49">
-        <v>20</v>
-      </c>
-      <c r="J49" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G49" t="s">
+        <v>22</v>
+      </c>
+      <c r="I49" t="s">
+        <v>26</v>
+      </c>
+      <c r="J49">
+        <v>20</v>
       </c>
       <c r="K49" t="b">
         <v>1</v>
       </c>
       <c r="L49" t="b">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <v>15</v>
-      </c>
-      <c r="O49" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q49" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M49" t="b">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>15</v>
+      </c>
+      <c r="P49" t="s">
+        <v>27</v>
       </c>
       <c r="R49" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>118</v>
       </c>
@@ -3029,40 +3182,43 @@
         <v>20</v>
       </c>
       <c r="E50" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F50" t="s">
-        <v>22</v>
-      </c>
-      <c r="H50" t="s">
-        <v>26</v>
-      </c>
-      <c r="I50">
-        <v>20</v>
-      </c>
-      <c r="J50" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G50" t="s">
+        <v>22</v>
+      </c>
+      <c r="I50" t="s">
+        <v>26</v>
+      </c>
+      <c r="J50">
+        <v>20</v>
       </c>
       <c r="K50" t="b">
         <v>1</v>
       </c>
       <c r="L50" t="b">
-        <v>0</v>
-      </c>
-      <c r="M50">
-        <v>15</v>
-      </c>
-      <c r="O50" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q50" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M50" t="b">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>15</v>
+      </c>
+      <c r="P50" t="s">
+        <v>27</v>
       </c>
       <c r="R50" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>120</v>
       </c>
@@ -3070,46 +3226,49 @@
         <v>119</v>
       </c>
       <c r="C51" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D51" t="s">
         <v>29</v>
       </c>
       <c r="E51" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F51" t="s">
-        <v>22</v>
-      </c>
-      <c r="H51" t="s">
-        <v>26</v>
-      </c>
-      <c r="I51">
-        <v>20</v>
-      </c>
-      <c r="J51" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G51" t="s">
+        <v>22</v>
+      </c>
+      <c r="I51" t="s">
+        <v>26</v>
+      </c>
+      <c r="J51">
+        <v>20</v>
       </c>
       <c r="K51" t="b">
         <v>1</v>
       </c>
       <c r="L51" t="b">
-        <v>0</v>
-      </c>
-      <c r="M51">
-        <v>15</v>
-      </c>
-      <c r="O51" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q51" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M51" t="b">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>15</v>
+      </c>
+      <c r="P51" t="s">
+        <v>27</v>
       </c>
       <c r="R51" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>121</v>
       </c>
@@ -3117,46 +3276,49 @@
         <v>119</v>
       </c>
       <c r="C52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D52" t="s">
         <v>62</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>63</v>
       </c>
-      <c r="E52" t="s">
-        <v>21</v>
-      </c>
       <c r="F52" t="s">
-        <v>22</v>
-      </c>
-      <c r="H52" t="s">
-        <v>26</v>
-      </c>
-      <c r="I52">
-        <v>20</v>
-      </c>
-      <c r="J52" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G52" t="s">
+        <v>22</v>
+      </c>
+      <c r="I52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J52">
+        <v>20</v>
       </c>
       <c r="K52" t="b">
         <v>1</v>
       </c>
       <c r="L52" t="b">
-        <v>0</v>
-      </c>
-      <c r="M52">
-        <v>15</v>
-      </c>
-      <c r="O52" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q52" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M52" t="b">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>15</v>
+      </c>
+      <c r="P52" t="s">
+        <v>27</v>
       </c>
       <c r="R52" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>122</v>
       </c>
@@ -3164,46 +3326,49 @@
         <v>119</v>
       </c>
       <c r="C53" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" t="s">
         <v>66</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>67</v>
       </c>
-      <c r="E53" t="s">
-        <v>21</v>
-      </c>
       <c r="F53" t="s">
-        <v>22</v>
-      </c>
-      <c r="H53" t="s">
-        <v>26</v>
-      </c>
-      <c r="I53">
-        <v>20</v>
-      </c>
-      <c r="J53" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G53" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" t="s">
+        <v>26</v>
+      </c>
+      <c r="J53">
+        <v>20</v>
       </c>
       <c r="K53" t="b">
         <v>1</v>
       </c>
       <c r="L53" t="b">
-        <v>0</v>
-      </c>
-      <c r="M53">
-        <v>15</v>
-      </c>
-      <c r="O53" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q53" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M53" t="b">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>15</v>
+      </c>
+      <c r="P53" t="s">
+        <v>27</v>
       </c>
       <c r="R53" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>123</v>
       </c>
@@ -3211,46 +3376,49 @@
         <v>119</v>
       </c>
       <c r="C54" t="s">
+        <v>20</v>
+      </c>
+      <c r="D54" t="s">
         <v>69</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>106</v>
       </c>
-      <c r="E54" t="s">
-        <v>21</v>
-      </c>
       <c r="F54" t="s">
-        <v>22</v>
-      </c>
-      <c r="H54" t="s">
-        <v>26</v>
-      </c>
-      <c r="I54">
-        <v>20</v>
-      </c>
-      <c r="J54" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G54" t="s">
+        <v>22</v>
+      </c>
+      <c r="I54" t="s">
+        <v>26</v>
+      </c>
+      <c r="J54">
+        <v>20</v>
       </c>
       <c r="K54" t="b">
         <v>1</v>
       </c>
       <c r="L54" t="b">
-        <v>0</v>
-      </c>
-      <c r="M54">
-        <v>15</v>
-      </c>
-      <c r="O54" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q54" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M54" t="b">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>15</v>
+      </c>
+      <c r="P54" t="s">
+        <v>27</v>
       </c>
       <c r="R54" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>124</v>
       </c>
@@ -3258,46 +3426,49 @@
         <v>119</v>
       </c>
       <c r="C55" t="s">
+        <v>20</v>
+      </c>
+      <c r="D55" t="s">
         <v>72</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>73</v>
       </c>
-      <c r="E55" t="s">
-        <v>21</v>
-      </c>
       <c r="F55" t="s">
-        <v>22</v>
-      </c>
-      <c r="H55" t="s">
-        <v>26</v>
-      </c>
-      <c r="I55">
-        <v>20</v>
-      </c>
-      <c r="J55" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G55" t="s">
+        <v>22</v>
+      </c>
+      <c r="I55" t="s">
+        <v>26</v>
+      </c>
+      <c r="J55">
+        <v>20</v>
       </c>
       <c r="K55" t="b">
         <v>1</v>
       </c>
       <c r="L55" t="b">
-        <v>0</v>
-      </c>
-      <c r="M55">
-        <v>15</v>
-      </c>
-      <c r="O55" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q55" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M55" t="b">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>15</v>
+      </c>
+      <c r="P55" t="s">
+        <v>27</v>
       </c>
       <c r="R55" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>125</v>
       </c>
@@ -3305,46 +3476,49 @@
         <v>119</v>
       </c>
       <c r="C56" t="s">
+        <v>20</v>
+      </c>
+      <c r="D56" t="s">
         <v>75</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>76</v>
       </c>
-      <c r="E56" t="s">
-        <v>21</v>
-      </c>
       <c r="F56" t="s">
-        <v>22</v>
-      </c>
-      <c r="H56" t="s">
-        <v>26</v>
-      </c>
-      <c r="I56">
-        <v>20</v>
-      </c>
-      <c r="J56" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G56" t="s">
+        <v>22</v>
+      </c>
+      <c r="I56" t="s">
+        <v>26</v>
+      </c>
+      <c r="J56">
+        <v>20</v>
       </c>
       <c r="K56" t="b">
         <v>1</v>
       </c>
       <c r="L56" t="b">
-        <v>0</v>
-      </c>
-      <c r="M56">
-        <v>15</v>
-      </c>
-      <c r="O56" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q56" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M56" t="b">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>15</v>
+      </c>
+      <c r="P56" t="s">
+        <v>27</v>
       </c>
       <c r="R56" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>126</v>
       </c>
@@ -3352,46 +3526,49 @@
         <v>119</v>
       </c>
       <c r="C57" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57" t="s">
         <v>78</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>79</v>
       </c>
-      <c r="E57" t="s">
-        <v>21</v>
-      </c>
       <c r="F57" t="s">
-        <v>22</v>
-      </c>
-      <c r="H57" t="s">
-        <v>26</v>
-      </c>
-      <c r="I57">
-        <v>20</v>
-      </c>
-      <c r="J57" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G57" t="s">
+        <v>22</v>
+      </c>
+      <c r="I57" t="s">
+        <v>26</v>
+      </c>
+      <c r="J57">
+        <v>20</v>
       </c>
       <c r="K57" t="b">
         <v>1</v>
       </c>
       <c r="L57" t="b">
-        <v>0</v>
-      </c>
-      <c r="M57">
-        <v>15</v>
-      </c>
-      <c r="O57" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q57" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M57" t="b">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>15</v>
+      </c>
+      <c r="P57" t="s">
+        <v>27</v>
       </c>
       <c r="R57" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>127</v>
       </c>
@@ -3399,46 +3576,49 @@
         <v>119</v>
       </c>
       <c r="C58" t="s">
+        <v>20</v>
+      </c>
+      <c r="D58" t="s">
         <v>81</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>82</v>
       </c>
-      <c r="E58" t="s">
-        <v>21</v>
-      </c>
       <c r="F58" t="s">
-        <v>22</v>
-      </c>
-      <c r="H58" t="s">
-        <v>26</v>
-      </c>
-      <c r="I58">
-        <v>20</v>
-      </c>
-      <c r="J58" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G58" t="s">
+        <v>22</v>
+      </c>
+      <c r="I58" t="s">
+        <v>26</v>
+      </c>
+      <c r="J58">
+        <v>20</v>
       </c>
       <c r="K58" t="b">
         <v>1</v>
       </c>
       <c r="L58" t="b">
-        <v>0</v>
-      </c>
-      <c r="M58">
-        <v>15</v>
-      </c>
-      <c r="O58" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q58" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M58" t="b">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>15</v>
+      </c>
+      <c r="P58" t="s">
+        <v>27</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>128</v>
       </c>
@@ -3446,46 +3626,49 @@
         <v>119</v>
       </c>
       <c r="C59" t="s">
+        <v>20</v>
+      </c>
+      <c r="D59" t="s">
         <v>84</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>85</v>
       </c>
-      <c r="E59" t="s">
-        <v>21</v>
-      </c>
       <c r="F59" t="s">
-        <v>22</v>
-      </c>
-      <c r="H59" t="s">
-        <v>26</v>
-      </c>
-      <c r="I59">
-        <v>20</v>
-      </c>
-      <c r="J59" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G59" t="s">
+        <v>22</v>
+      </c>
+      <c r="I59" t="s">
+        <v>26</v>
+      </c>
+      <c r="J59">
+        <v>20</v>
       </c>
       <c r="K59" t="b">
         <v>1</v>
       </c>
       <c r="L59" t="b">
-        <v>0</v>
-      </c>
-      <c r="M59">
-        <v>15</v>
-      </c>
-      <c r="O59" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q59" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M59" t="b">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>15</v>
+      </c>
+      <c r="P59" t="s">
+        <v>27</v>
       </c>
       <c r="R59" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>129</v>
       </c>
@@ -3493,46 +3676,49 @@
         <v>119</v>
       </c>
       <c r="C60" t="s">
+        <v>20</v>
+      </c>
+      <c r="D60" t="s">
         <v>86</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>113</v>
       </c>
-      <c r="E60" t="s">
-        <v>21</v>
-      </c>
       <c r="F60" t="s">
-        <v>22</v>
-      </c>
-      <c r="H60" t="s">
-        <v>26</v>
-      </c>
-      <c r="I60">
-        <v>20</v>
-      </c>
-      <c r="J60" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G60" t="s">
+        <v>22</v>
+      </c>
+      <c r="I60" t="s">
+        <v>26</v>
+      </c>
+      <c r="J60">
+        <v>20</v>
       </c>
       <c r="K60" t="b">
         <v>1</v>
       </c>
       <c r="L60" t="b">
-        <v>0</v>
-      </c>
-      <c r="M60">
-        <v>15</v>
-      </c>
-      <c r="O60" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q60" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M60" t="b">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>15</v>
+      </c>
+      <c r="P60" t="s">
+        <v>27</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>130</v>
       </c>
@@ -3540,46 +3726,49 @@
         <v>119</v>
       </c>
       <c r="C61" t="s">
+        <v>20</v>
+      </c>
+      <c r="D61" t="s">
         <v>89</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>90</v>
       </c>
-      <c r="E61" t="s">
-        <v>21</v>
-      </c>
       <c r="F61" t="s">
-        <v>22</v>
-      </c>
-      <c r="H61" t="s">
-        <v>26</v>
-      </c>
-      <c r="I61">
-        <v>20</v>
-      </c>
-      <c r="J61" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G61" t="s">
+        <v>22</v>
+      </c>
+      <c r="I61" t="s">
+        <v>26</v>
+      </c>
+      <c r="J61">
+        <v>20</v>
       </c>
       <c r="K61" t="b">
         <v>1</v>
       </c>
       <c r="L61" t="b">
-        <v>0</v>
-      </c>
-      <c r="M61">
-        <v>15</v>
-      </c>
-      <c r="O61" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q61" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M61" t="b">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>15</v>
+      </c>
+      <c r="P61" t="s">
+        <v>27</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>131</v>
       </c>
@@ -3587,46 +3776,49 @@
         <v>119</v>
       </c>
       <c r="C62" t="s">
+        <v>20</v>
+      </c>
+      <c r="D62" t="s">
         <v>92</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>93</v>
       </c>
-      <c r="E62" t="s">
-        <v>21</v>
-      </c>
       <c r="F62" t="s">
-        <v>22</v>
-      </c>
-      <c r="H62" t="s">
-        <v>26</v>
-      </c>
-      <c r="I62">
-        <v>20</v>
-      </c>
-      <c r="J62" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G62" t="s">
+        <v>22</v>
+      </c>
+      <c r="I62" t="s">
+        <v>26</v>
+      </c>
+      <c r="J62">
+        <v>20</v>
       </c>
       <c r="K62" t="b">
         <v>1</v>
       </c>
       <c r="L62" t="b">
-        <v>0</v>
-      </c>
-      <c r="M62">
-        <v>15</v>
-      </c>
-      <c r="O62" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q62" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M62" t="b">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>15</v>
+      </c>
+      <c r="P62" t="s">
+        <v>27</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>132</v>
       </c>
@@ -3634,46 +3826,49 @@
         <v>119</v>
       </c>
       <c r="C63" t="s">
+        <v>20</v>
+      </c>
+      <c r="D63" t="s">
         <v>95</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>96</v>
       </c>
-      <c r="E63" t="s">
-        <v>21</v>
-      </c>
       <c r="F63" t="s">
-        <v>22</v>
-      </c>
-      <c r="H63" t="s">
-        <v>26</v>
-      </c>
-      <c r="I63">
-        <v>20</v>
-      </c>
-      <c r="J63" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G63" t="s">
+        <v>22</v>
+      </c>
+      <c r="I63" t="s">
+        <v>26</v>
+      </c>
+      <c r="J63">
+        <v>20</v>
       </c>
       <c r="K63" t="b">
         <v>1</v>
       </c>
       <c r="L63" t="b">
-        <v>0</v>
-      </c>
-      <c r="M63">
-        <v>15</v>
-      </c>
-      <c r="O63" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q63" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M63" t="b">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>15</v>
+      </c>
+      <c r="P63" t="s">
+        <v>27</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>133</v>
       </c>
@@ -3681,46 +3876,49 @@
         <v>119</v>
       </c>
       <c r="C64" t="s">
+        <v>20</v>
+      </c>
+      <c r="D64" t="s">
         <v>98</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>99</v>
       </c>
-      <c r="E64" t="s">
-        <v>21</v>
-      </c>
       <c r="F64" t="s">
-        <v>22</v>
-      </c>
-      <c r="H64" t="s">
-        <v>26</v>
-      </c>
-      <c r="I64">
-        <v>20</v>
-      </c>
-      <c r="J64" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G64" t="s">
+        <v>22</v>
+      </c>
+      <c r="I64" t="s">
+        <v>26</v>
+      </c>
+      <c r="J64">
+        <v>20</v>
       </c>
       <c r="K64" t="b">
         <v>1</v>
       </c>
       <c r="L64" t="b">
-        <v>0</v>
-      </c>
-      <c r="M64">
-        <v>15</v>
-      </c>
-      <c r="O64" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q64" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M64" t="b">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>15</v>
+      </c>
+      <c r="P64" t="s">
+        <v>27</v>
       </c>
       <c r="R64" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>134</v>
       </c>
@@ -3734,40 +3932,43 @@
         <v>20</v>
       </c>
       <c r="E65" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F65" t="s">
-        <v>22</v>
-      </c>
-      <c r="H65" t="s">
-        <v>26</v>
-      </c>
-      <c r="I65">
-        <v>20</v>
-      </c>
-      <c r="J65" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G65" t="s">
+        <v>22</v>
+      </c>
+      <c r="I65" t="s">
+        <v>26</v>
+      </c>
+      <c r="J65">
+        <v>20</v>
       </c>
       <c r="K65" t="b">
         <v>1</v>
       </c>
       <c r="L65" t="b">
-        <v>0</v>
-      </c>
-      <c r="M65">
-        <v>15</v>
-      </c>
-      <c r="O65" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q65" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M65" t="b">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>15</v>
+      </c>
+      <c r="P65" t="s">
+        <v>27</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>136</v>
       </c>
@@ -3775,46 +3976,49 @@
         <v>135</v>
       </c>
       <c r="C66" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D66" t="s">
         <v>29</v>
       </c>
       <c r="E66" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F66" t="s">
-        <v>22</v>
-      </c>
-      <c r="H66" t="s">
-        <v>26</v>
-      </c>
-      <c r="I66">
-        <v>20</v>
-      </c>
-      <c r="J66" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G66" t="s">
+        <v>22</v>
+      </c>
+      <c r="I66" t="s">
+        <v>26</v>
+      </c>
+      <c r="J66">
+        <v>20</v>
       </c>
       <c r="K66" t="b">
         <v>1</v>
       </c>
       <c r="L66" t="b">
-        <v>0</v>
-      </c>
-      <c r="M66">
-        <v>15</v>
-      </c>
-      <c r="O66" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q66" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M66" t="b">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>15</v>
+      </c>
+      <c r="P66" t="s">
+        <v>27</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>137</v>
       </c>
@@ -3822,46 +4026,49 @@
         <v>135</v>
       </c>
       <c r="C67" t="s">
+        <v>20</v>
+      </c>
+      <c r="D67" t="s">
         <v>62</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>63</v>
       </c>
-      <c r="E67" t="s">
-        <v>21</v>
-      </c>
       <c r="F67" t="s">
-        <v>22</v>
-      </c>
-      <c r="H67" t="s">
-        <v>26</v>
-      </c>
-      <c r="I67">
-        <v>20</v>
-      </c>
-      <c r="J67" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G67" t="s">
+        <v>22</v>
+      </c>
+      <c r="I67" t="s">
+        <v>26</v>
+      </c>
+      <c r="J67">
+        <v>20</v>
       </c>
       <c r="K67" t="b">
         <v>1</v>
       </c>
       <c r="L67" t="b">
-        <v>0</v>
-      </c>
-      <c r="M67">
-        <v>15</v>
-      </c>
-      <c r="O67" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q67" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M67" t="b">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>15</v>
+      </c>
+      <c r="P67" t="s">
+        <v>27</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>138</v>
       </c>
@@ -3869,46 +4076,49 @@
         <v>135</v>
       </c>
       <c r="C68" t="s">
+        <v>20</v>
+      </c>
+      <c r="D68" t="s">
         <v>66</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>67</v>
       </c>
-      <c r="E68" t="s">
-        <v>21</v>
-      </c>
       <c r="F68" t="s">
-        <v>22</v>
-      </c>
-      <c r="H68" t="s">
-        <v>26</v>
-      </c>
-      <c r="I68">
-        <v>20</v>
-      </c>
-      <c r="J68" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G68" t="s">
+        <v>22</v>
+      </c>
+      <c r="I68" t="s">
+        <v>26</v>
+      </c>
+      <c r="J68">
+        <v>20</v>
       </c>
       <c r="K68" t="b">
         <v>1</v>
       </c>
       <c r="L68" t="b">
-        <v>0</v>
-      </c>
-      <c r="M68">
-        <v>15</v>
-      </c>
-      <c r="O68" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q68" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M68" t="b">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>15</v>
+      </c>
+      <c r="P68" t="s">
+        <v>27</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>139</v>
       </c>
@@ -3916,46 +4126,49 @@
         <v>135</v>
       </c>
       <c r="C69" t="s">
+        <v>20</v>
+      </c>
+      <c r="D69" t="s">
         <v>69</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>106</v>
       </c>
-      <c r="E69" t="s">
-        <v>21</v>
-      </c>
       <c r="F69" t="s">
-        <v>22</v>
-      </c>
-      <c r="H69" t="s">
-        <v>26</v>
-      </c>
-      <c r="I69">
-        <v>20</v>
-      </c>
-      <c r="J69" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G69" t="s">
+        <v>22</v>
+      </c>
+      <c r="I69" t="s">
+        <v>26</v>
+      </c>
+      <c r="J69">
+        <v>20</v>
       </c>
       <c r="K69" t="b">
         <v>1</v>
       </c>
       <c r="L69" t="b">
-        <v>0</v>
-      </c>
-      <c r="M69">
-        <v>15</v>
-      </c>
-      <c r="O69" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q69" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M69" t="b">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>15</v>
+      </c>
+      <c r="P69" t="s">
+        <v>27</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>140</v>
       </c>
@@ -3963,46 +4176,49 @@
         <v>135</v>
       </c>
       <c r="C70" t="s">
+        <v>20</v>
+      </c>
+      <c r="D70" t="s">
         <v>72</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>73</v>
       </c>
-      <c r="E70" t="s">
-        <v>21</v>
-      </c>
       <c r="F70" t="s">
-        <v>22</v>
-      </c>
-      <c r="H70" t="s">
-        <v>26</v>
-      </c>
-      <c r="I70">
-        <v>20</v>
-      </c>
-      <c r="J70" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G70" t="s">
+        <v>22</v>
+      </c>
+      <c r="I70" t="s">
+        <v>26</v>
+      </c>
+      <c r="J70">
+        <v>20</v>
       </c>
       <c r="K70" t="b">
         <v>1</v>
       </c>
       <c r="L70" t="b">
-        <v>0</v>
-      </c>
-      <c r="M70">
-        <v>15</v>
-      </c>
-      <c r="O70" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q70" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M70" t="b">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>15</v>
+      </c>
+      <c r="P70" t="s">
+        <v>27</v>
       </c>
       <c r="R70" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>141</v>
       </c>
@@ -4010,46 +4226,49 @@
         <v>135</v>
       </c>
       <c r="C71" t="s">
+        <v>20</v>
+      </c>
+      <c r="D71" t="s">
         <v>75</v>
       </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>76</v>
       </c>
-      <c r="E71" t="s">
-        <v>21</v>
-      </c>
       <c r="F71" t="s">
-        <v>22</v>
-      </c>
-      <c r="H71" t="s">
-        <v>26</v>
-      </c>
-      <c r="I71">
-        <v>20</v>
-      </c>
-      <c r="J71" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G71" t="s">
+        <v>22</v>
+      </c>
+      <c r="I71" t="s">
+        <v>26</v>
+      </c>
+      <c r="J71">
+        <v>20</v>
       </c>
       <c r="K71" t="b">
         <v>1</v>
       </c>
       <c r="L71" t="b">
-        <v>0</v>
-      </c>
-      <c r="M71">
-        <v>15</v>
-      </c>
-      <c r="O71" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q71" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M71" t="b">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>15</v>
+      </c>
+      <c r="P71" t="s">
+        <v>27</v>
       </c>
       <c r="R71" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>142</v>
       </c>
@@ -4057,46 +4276,49 @@
         <v>135</v>
       </c>
       <c r="C72" t="s">
+        <v>20</v>
+      </c>
+      <c r="D72" t="s">
         <v>78</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>79</v>
       </c>
-      <c r="E72" t="s">
-        <v>21</v>
-      </c>
       <c r="F72" t="s">
-        <v>22</v>
-      </c>
-      <c r="H72" t="s">
-        <v>26</v>
-      </c>
-      <c r="I72">
-        <v>20</v>
-      </c>
-      <c r="J72" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G72" t="s">
+        <v>22</v>
+      </c>
+      <c r="I72" t="s">
+        <v>26</v>
+      </c>
+      <c r="J72">
+        <v>20</v>
       </c>
       <c r="K72" t="b">
         <v>1</v>
       </c>
       <c r="L72" t="b">
-        <v>0</v>
-      </c>
-      <c r="M72">
-        <v>15</v>
-      </c>
-      <c r="O72" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q72" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M72" t="b">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>15</v>
+      </c>
+      <c r="P72" t="s">
+        <v>27</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>143</v>
       </c>
@@ -4104,46 +4326,49 @@
         <v>135</v>
       </c>
       <c r="C73" t="s">
+        <v>20</v>
+      </c>
+      <c r="D73" t="s">
         <v>81</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>82</v>
       </c>
-      <c r="E73" t="s">
-        <v>21</v>
-      </c>
       <c r="F73" t="s">
-        <v>22</v>
-      </c>
-      <c r="H73" t="s">
-        <v>26</v>
-      </c>
-      <c r="I73">
-        <v>20</v>
-      </c>
-      <c r="J73" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G73" t="s">
+        <v>22</v>
+      </c>
+      <c r="I73" t="s">
+        <v>26</v>
+      </c>
+      <c r="J73">
+        <v>20</v>
       </c>
       <c r="K73" t="b">
         <v>1</v>
       </c>
       <c r="L73" t="b">
-        <v>0</v>
-      </c>
-      <c r="M73">
-        <v>15</v>
-      </c>
-      <c r="O73" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q73" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M73" t="b">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>15</v>
+      </c>
+      <c r="P73" t="s">
+        <v>27</v>
       </c>
       <c r="R73" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>144</v>
       </c>
@@ -4151,46 +4376,49 @@
         <v>135</v>
       </c>
       <c r="C74" t="s">
+        <v>20</v>
+      </c>
+      <c r="D74" t="s">
         <v>84</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>85</v>
       </c>
-      <c r="E74" t="s">
-        <v>21</v>
-      </c>
       <c r="F74" t="s">
-        <v>22</v>
-      </c>
-      <c r="H74" t="s">
-        <v>26</v>
-      </c>
-      <c r="I74">
-        <v>20</v>
-      </c>
-      <c r="J74" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G74" t="s">
+        <v>22</v>
+      </c>
+      <c r="I74" t="s">
+        <v>26</v>
+      </c>
+      <c r="J74">
+        <v>20</v>
       </c>
       <c r="K74" t="b">
         <v>1</v>
       </c>
       <c r="L74" t="b">
-        <v>0</v>
-      </c>
-      <c r="M74">
-        <v>15</v>
-      </c>
-      <c r="O74" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q74" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M74" t="b">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>15</v>
+      </c>
+      <c r="P74" t="s">
+        <v>27</v>
       </c>
       <c r="R74" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>145</v>
       </c>
@@ -4198,46 +4426,49 @@
         <v>135</v>
       </c>
       <c r="C75" t="s">
+        <v>20</v>
+      </c>
+      <c r="D75" t="s">
         <v>86</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
         <v>113</v>
       </c>
-      <c r="E75" t="s">
-        <v>21</v>
-      </c>
       <c r="F75" t="s">
-        <v>22</v>
-      </c>
-      <c r="H75" t="s">
-        <v>26</v>
-      </c>
-      <c r="I75">
-        <v>20</v>
-      </c>
-      <c r="J75" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G75" t="s">
+        <v>22</v>
+      </c>
+      <c r="I75" t="s">
+        <v>26</v>
+      </c>
+      <c r="J75">
+        <v>20</v>
       </c>
       <c r="K75" t="b">
         <v>1</v>
       </c>
       <c r="L75" t="b">
-        <v>0</v>
-      </c>
-      <c r="M75">
-        <v>15</v>
-      </c>
-      <c r="O75" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q75" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M75" t="b">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>15</v>
+      </c>
+      <c r="P75" t="s">
+        <v>27</v>
       </c>
       <c r="R75" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>146</v>
       </c>
@@ -4245,46 +4476,49 @@
         <v>135</v>
       </c>
       <c r="C76" t="s">
+        <v>20</v>
+      </c>
+      <c r="D76" t="s">
         <v>89</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>90</v>
       </c>
-      <c r="E76" t="s">
-        <v>21</v>
-      </c>
       <c r="F76" t="s">
-        <v>22</v>
-      </c>
-      <c r="H76" t="s">
-        <v>26</v>
-      </c>
-      <c r="I76">
-        <v>20</v>
-      </c>
-      <c r="J76" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G76" t="s">
+        <v>22</v>
+      </c>
+      <c r="I76" t="s">
+        <v>26</v>
+      </c>
+      <c r="J76">
+        <v>20</v>
       </c>
       <c r="K76" t="b">
         <v>1</v>
       </c>
       <c r="L76" t="b">
-        <v>0</v>
-      </c>
-      <c r="M76">
-        <v>15</v>
-      </c>
-      <c r="O76" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q76" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M76" t="b">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>15</v>
+      </c>
+      <c r="P76" t="s">
+        <v>27</v>
       </c>
       <c r="R76" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>147</v>
       </c>
@@ -4292,46 +4526,49 @@
         <v>135</v>
       </c>
       <c r="C77" t="s">
+        <v>20</v>
+      </c>
+      <c r="D77" t="s">
         <v>92</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>93</v>
       </c>
-      <c r="E77" t="s">
-        <v>21</v>
-      </c>
       <c r="F77" t="s">
-        <v>22</v>
-      </c>
-      <c r="H77" t="s">
-        <v>26</v>
-      </c>
-      <c r="I77">
-        <v>20</v>
-      </c>
-      <c r="J77" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G77" t="s">
+        <v>22</v>
+      </c>
+      <c r="I77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J77">
+        <v>20</v>
       </c>
       <c r="K77" t="b">
         <v>1</v>
       </c>
       <c r="L77" t="b">
-        <v>0</v>
-      </c>
-      <c r="M77">
-        <v>15</v>
-      </c>
-      <c r="O77" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q77" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M77" t="b">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>15</v>
+      </c>
+      <c r="P77" t="s">
+        <v>27</v>
       </c>
       <c r="R77" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>148</v>
       </c>
@@ -4339,46 +4576,49 @@
         <v>135</v>
       </c>
       <c r="C78" t="s">
+        <v>20</v>
+      </c>
+      <c r="D78" t="s">
         <v>95</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>96</v>
       </c>
-      <c r="E78" t="s">
-        <v>21</v>
-      </c>
       <c r="F78" t="s">
-        <v>22</v>
-      </c>
-      <c r="H78" t="s">
-        <v>26</v>
-      </c>
-      <c r="I78">
-        <v>20</v>
-      </c>
-      <c r="J78" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G78" t="s">
+        <v>22</v>
+      </c>
+      <c r="I78" t="s">
+        <v>26</v>
+      </c>
+      <c r="J78">
+        <v>20</v>
       </c>
       <c r="K78" t="b">
         <v>1</v>
       </c>
       <c r="L78" t="b">
-        <v>0</v>
-      </c>
-      <c r="M78">
-        <v>15</v>
-      </c>
-      <c r="O78" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q78" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M78" t="b">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>15</v>
+      </c>
+      <c r="P78" t="s">
+        <v>27</v>
       </c>
       <c r="R78" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>149</v>
       </c>
@@ -4386,51 +4626,54 @@
         <v>135</v>
       </c>
       <c r="C79" t="s">
+        <v>20</v>
+      </c>
+      <c r="D79" t="s">
         <v>98</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>99</v>
       </c>
-      <c r="E79" t="s">
-        <v>21</v>
-      </c>
       <c r="F79" t="s">
-        <v>22</v>
-      </c>
-      <c r="H79" t="s">
-        <v>26</v>
-      </c>
-      <c r="I79">
-        <v>20</v>
-      </c>
-      <c r="J79" t="b">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="G79" t="s">
+        <v>22</v>
+      </c>
+      <c r="I79" t="s">
+        <v>26</v>
+      </c>
+      <c r="J79">
+        <v>20</v>
       </c>
       <c r="K79" t="b">
         <v>1</v>
       </c>
       <c r="L79" t="b">
-        <v>0</v>
-      </c>
-      <c r="M79">
-        <v>15</v>
-      </c>
-      <c r="O79" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q79" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M79" t="b">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>15</v>
+      </c>
+      <c r="P79" t="s">
+        <v>27</v>
       </c>
       <c r="R79" t="b">
+        <v>0</v>
+      </c>
+      <c r="S79" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D8" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D9" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D18" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="E5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E8" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="E9" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="E18" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscarcuellar/ocn/media/apify_client/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E462C443-348B-DD4F-B163-A03F890E3555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C123BBC-C9DD-BE41-9402-E65AF901FCB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="31920" windowHeight="20780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="167">
   <si>
     <t>task_id</t>
   </si>
@@ -515,6 +515,12 @@
   </si>
   <si>
     <t>Poder Ciudadano Radio</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/FeliferMaciasO</t>
+  </si>
+  <si>
+    <t>FeliFer Macías</t>
   </si>
 </sst>
 </file>
@@ -897,7 +903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U82"/>
+  <dimension ref="A1:U83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="19.6640625" customWidth="1"/>
@@ -4864,6 +4870,50 @@
         <v>0</v>
       </c>
       <c r="T82" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>83</v>
+      </c>
+      <c r="B83" t="s">
+        <v>30</v>
+      </c>
+      <c r="C83" t="s">
+        <v>150</v>
+      </c>
+      <c r="D83" t="s">
+        <v>166</v>
+      </c>
+      <c r="E83" t="s">
+        <v>165</v>
+      </c>
+      <c r="F83">
+        <v>97000</v>
+      </c>
+      <c r="J83" t="s">
+        <v>26</v>
+      </c>
+      <c r="K83">
+        <v>30</v>
+      </c>
+      <c r="L83" t="b">
+        <v>1</v>
+      </c>
+      <c r="M83" t="b">
+        <v>1</v>
+      </c>
+      <c r="N83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O83">
+        <v>15</v>
+      </c>
+      <c r="S83" t="b">
+        <v>0</v>
+      </c>
+      <c r="T83" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscarcuellar/ocn/media/apify_client/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C123BBC-C9DD-BE41-9402-E65AF901FCB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8681C6-971E-3E42-AA81-D6DE234F5BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="31920" windowHeight="20780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="38980" windowHeight="26620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tasks" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="167">
   <si>
     <t>task_id</t>
   </si>
@@ -903,7 +903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U83"/>
+  <dimension ref="A1:U84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="19.6640625" customWidth="1"/>
@@ -1140,7 +1140,7 @@
         <v>26</v>
       </c>
       <c r="K5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -1184,7 +1184,7 @@
         <v>26</v>
       </c>
       <c r="K6">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L6" t="b">
         <v>1</v>
@@ -4914,6 +4914,47 @@
         <v>0</v>
       </c>
       <c r="T83" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>84</v>
+      </c>
+      <c r="B84" t="s">
+        <v>100</v>
+      </c>
+      <c r="C84" t="s">
+        <v>150</v>
+      </c>
+      <c r="D84" t="s">
+        <v>150</v>
+      </c>
+      <c r="E84" t="s">
+        <v>150</v>
+      </c>
+      <c r="J84" t="s">
+        <v>26</v>
+      </c>
+      <c r="K84">
+        <v>5</v>
+      </c>
+      <c r="L84" t="b">
+        <v>1</v>
+      </c>
+      <c r="M84" t="b">
+        <v>1</v>
+      </c>
+      <c r="N84" t="b">
+        <v>1</v>
+      </c>
+      <c r="O84">
+        <v>15</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscarcuellar/ocn/media/apify_client/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8681C6-971E-3E42-AA81-D6DE234F5BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C6E10D-FB04-1447-88D5-598FA7FF75D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="38980" windowHeight="26620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="169">
   <si>
     <t>task_id</t>
   </si>
@@ -521,6 +521,12 @@
   </si>
   <si>
     <t>FeliFer Macías</t>
+  </si>
+  <si>
+    <t>{"get_comments_after_likes": 100, "enrich_author_after_likes": 100}</t>
+  </si>
+  <si>
+    <t>Conserva sólo las publicaciones que hablen de eventos o temas de interés común en el estado o ciudad de Querétaro (en general, temas que puedan ser de interés para el gobierno, ejemplo no exhaustivo: Emergencias, infraestructura, eventos culturales, servicios públicos, seguridad, ... entre otros). Elimina las preguntas de usuarios, ofertas de ventas, saludos, etc,)</t>
   </si>
 </sst>
 </file>
@@ -4785,7 +4791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>81</v>
       </c>
@@ -4829,7 +4835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>82</v>
       </c>
@@ -4873,7 +4879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>83</v>
       </c>
@@ -4917,7 +4923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>84</v>
       </c>
@@ -4937,7 +4943,7 @@
         <v>26</v>
       </c>
       <c r="K84">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="L84" t="b">
         <v>1</v>
@@ -4951,11 +4957,17 @@
       <c r="O84">
         <v>15</v>
       </c>
+      <c r="Q84" t="s">
+        <v>168</v>
+      </c>
       <c r="S84" t="b">
         <v>1</v>
       </c>
       <c r="T84" t="b">
         <v>1</v>
+      </c>
+      <c r="U84" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscarcuellar/ocn/media/apify_client/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C6E10D-FB04-1447-88D5-598FA7FF75D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFA1D13-B1B2-334F-984E-A99A98EF73A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="38980" windowHeight="26620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="31920" windowHeight="20780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tasks" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="177">
   <si>
     <t>task_id</t>
   </si>
@@ -527,6 +540,30 @@
   </si>
   <si>
     <t>Conserva sólo las publicaciones que hablen de eventos o temas de interés común en el estado o ciudad de Querétaro (en general, temas que puedan ser de interés para el gobierno, ejemplo no exhaustivo: Emergencias, infraestructura, eventos culturales, servicios públicos, seguridad, ... entre otros). Elimina las preguntas de usuarios, ofertas de ventas, saludos, etc,)</t>
+  </si>
+  <si>
+    <t>felifer</t>
+  </si>
+  <si>
+    <t>FeliFer Macías - Search</t>
+  </si>
+  <si>
+    <t>Conserva sólo las publicaciones que mencionen o hablen del alcalde de querétaro Felifer Macías (Felipe Fernando Macías Olvera)</t>
+  </si>
+  <si>
+    <t>chahin kuri</t>
+  </si>
+  <si>
+    <t>Hugo Chahín Kuri - Search</t>
+  </si>
+  <si>
+    <t>Conserva sólo las publicaciones que mencionen o hablen del alcalde de orizaba Hugo Chahín Kuri</t>
+  </si>
+  <si>
+    <t>Zona Fest</t>
+  </si>
+  <si>
+    <t>zona fest</t>
   </si>
 </sst>
 </file>
@@ -909,7 +946,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U84"/>
+  <dimension ref="A1:U87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="19.6640625" customWidth="1"/>
@@ -1234,7 +1271,7 @@
         <v>26</v>
       </c>
       <c r="K7">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
@@ -1278,7 +1315,7 @@
         <v>26</v>
       </c>
       <c r="K8">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
@@ -1322,7 +1359,7 @@
         <v>26</v>
       </c>
       <c r="K9">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
@@ -4770,7 +4807,7 @@
         <v>26</v>
       </c>
       <c r="K80">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L80" t="b">
         <v>1</v>
@@ -4814,7 +4851,7 @@
         <v>26</v>
       </c>
       <c r="K81">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L81" t="b">
         <v>1</v>
@@ -4858,7 +4895,7 @@
         <v>26</v>
       </c>
       <c r="K82">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L82" t="b">
         <v>1</v>
@@ -4902,7 +4939,7 @@
         <v>26</v>
       </c>
       <c r="K83">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L83" t="b">
         <v>1</v>
@@ -4967,6 +5004,147 @@
         <v>1</v>
       </c>
       <c r="U84" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>85</v>
+      </c>
+      <c r="B85" t="s">
+        <v>100</v>
+      </c>
+      <c r="C85" t="s">
+        <v>150</v>
+      </c>
+      <c r="D85" t="s">
+        <v>170</v>
+      </c>
+      <c r="E85" t="s">
+        <v>169</v>
+      </c>
+      <c r="J85" t="s">
+        <v>26</v>
+      </c>
+      <c r="K85">
+        <v>50</v>
+      </c>
+      <c r="L85" t="b">
+        <v>1</v>
+      </c>
+      <c r="M85" t="b">
+        <v>1</v>
+      </c>
+      <c r="N85" t="b">
+        <v>1</v>
+      </c>
+      <c r="O85">
+        <v>15</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>171</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="b">
+        <v>1</v>
+      </c>
+      <c r="U85" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>86</v>
+      </c>
+      <c r="B86" t="s">
+        <v>100</v>
+      </c>
+      <c r="C86" t="s">
+        <v>151</v>
+      </c>
+      <c r="D86" t="s">
+        <v>173</v>
+      </c>
+      <c r="E86" t="s">
+        <v>172</v>
+      </c>
+      <c r="J86" t="s">
+        <v>26</v>
+      </c>
+      <c r="K86">
+        <v>50</v>
+      </c>
+      <c r="L86" t="b">
+        <v>1</v>
+      </c>
+      <c r="M86" t="b">
+        <v>1</v>
+      </c>
+      <c r="N86" t="b">
+        <v>1</v>
+      </c>
+      <c r="O86">
+        <v>15</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>174</v>
+      </c>
+      <c r="S86" t="b">
+        <v>1</v>
+      </c>
+      <c r="T86" t="b">
+        <v>1</v>
+      </c>
+      <c r="U86" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>84</v>
+      </c>
+      <c r="B87" t="s">
+        <v>100</v>
+      </c>
+      <c r="C87" t="s">
+        <v>150</v>
+      </c>
+      <c r="D87" t="s">
+        <v>175</v>
+      </c>
+      <c r="E87" t="s">
+        <v>176</v>
+      </c>
+      <c r="J87" t="s">
+        <v>26</v>
+      </c>
+      <c r="K87">
+        <v>50</v>
+      </c>
+      <c r="L87" t="b">
+        <v>1</v>
+      </c>
+      <c r="M87" t="b">
+        <v>1</v>
+      </c>
+      <c r="N87" t="b">
+        <v>1</v>
+      </c>
+      <c r="O87">
+        <v>15</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>168</v>
+      </c>
+      <c r="S87" t="b">
+        <v>1</v>
+      </c>
+      <c r="T87" t="b">
+        <v>1</v>
+      </c>
+      <c r="U87" t="s">
         <v>167</v>
       </c>
     </row>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscarcuellar/ocn/media/apify_client/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFA1D13-B1B2-334F-984E-A99A98EF73A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA315F9B-B1C7-4B49-B3FC-FDC8052D3668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="31920" windowHeight="20780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6680" yWindow="700" windowWidth="38980" windowHeight="26620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tasks" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="181">
   <si>
     <t>task_id</t>
   </si>
@@ -564,6 +564,18 @@
   </si>
   <si>
     <t>zona fest</t>
+  </si>
+  <si>
+    <t>Conserva sólo las publicaciones que hablen del evento Zona Fest en Querétaro, o temas relacionados</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>{"timeframe":"7d","enrich":true}</t>
+  </si>
+  <si>
+    <t>update_existing</t>
   </si>
 </sst>
 </file>
@@ -946,7 +958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U87"/>
+  <dimension ref="A1:V88"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="19.6640625" customWidth="1"/>
@@ -954,7 +966,7 @@
     <col min="6" max="6" width="13.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1018,8 +1030,11 @@
       <c r="U1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1054,7 +1069,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1104,7 +1119,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1154,7 +1169,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1204,7 +1219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1248,7 +1263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1292,7 +1307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1336,7 +1351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1380,7 +1395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1421,7 +1436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1462,7 +1477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1503,7 +1518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1544,7 +1559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1585,7 +1600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1626,7 +1641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4828,7 +4843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>81</v>
       </c>
@@ -4872,7 +4887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>82</v>
       </c>
@@ -4916,7 +4931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>83</v>
       </c>
@@ -4960,7 +4975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>84</v>
       </c>
@@ -5007,7 +5022,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>85</v>
       </c>
@@ -5054,7 +5069,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>86</v>
       </c>
@@ -5101,9 +5116,9 @@
         <v>167</v>
       </c>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A87">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B87" t="s">
         <v>100</v>
@@ -5133,10 +5148,10 @@
         <v>1</v>
       </c>
       <c r="O87">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="Q87" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="S87" t="b">
         <v>1</v>
@@ -5146,6 +5161,50 @@
       </c>
       <c r="U87" t="s">
         <v>167</v>
+      </c>
+      <c r="V87" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>88</v>
+      </c>
+      <c r="B88" t="s">
+        <v>19</v>
+      </c>
+      <c r="C88" t="s">
+        <v>150</v>
+      </c>
+      <c r="D88" t="s">
+        <v>175</v>
+      </c>
+      <c r="E88" t="s">
+        <v>175</v>
+      </c>
+      <c r="G88" t="s">
+        <v>21</v>
+      </c>
+      <c r="H88" t="s">
+        <v>22</v>
+      </c>
+      <c r="J88" t="s">
+        <v>178</v>
+      </c>
+      <c r="K88">
+        <v>50</v>
+      </c>
+      <c r="L88" t="b">
+        <v>1</v>
+      </c>
+      <c r="M88" t="b">
+        <v>1</v>
+      </c>
+      <c r="N88" t="b">
+        <v>0</v>
+      </c>
+      <c r="U88" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscarcuellar/ocn/media/apify_client/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA315F9B-B1C7-4B49-B3FC-FDC8052D3668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2DEF5D-F99A-2949-AF75-909CB3812875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6680" yWindow="700" windowWidth="38980" windowHeight="26620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6680" yWindow="700" windowWidth="32860" windowHeight="26620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tasks" sheetId="1" r:id="rId1"/>
@@ -5136,7 +5136,7 @@
         <v>26</v>
       </c>
       <c r="K87">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L87" t="b">
         <v>1</v>
@@ -5192,7 +5192,7 @@
         <v>178</v>
       </c>
       <c r="K88">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L88" t="b">
         <v>1</v>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscarcuellar/ocn/media/apify_client/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2DEF5D-F99A-2949-AF75-909CB3812875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B0D6EC-1CB1-484D-B240-0B00C83F9422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6680" yWindow="700" windowWidth="32860" windowHeight="26620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="184">
   <si>
     <t>task_id</t>
   </si>
@@ -576,6 +576,15 @@
   </si>
   <si>
     <t>update_existing</t>
+  </si>
+  <si>
+    <t>mexicozonafest</t>
+  </si>
+  <si>
+    <t>zonafest</t>
+  </si>
+  <si>
+    <t>tiktok_posts</t>
   </si>
 </sst>
 </file>
@@ -958,7 +967,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V88"/>
+  <dimension ref="A1:V91"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="19.6640625" customWidth="1"/>
@@ -5205,6 +5214,153 @@
       </c>
       <c r="U88" t="s">
         <v>179</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>89</v>
+      </c>
+      <c r="B89" t="s">
+        <v>100</v>
+      </c>
+      <c r="C89" t="s">
+        <v>150</v>
+      </c>
+      <c r="D89" t="s">
+        <v>175</v>
+      </c>
+      <c r="E89" t="s">
+        <v>181</v>
+      </c>
+      <c r="J89" t="s">
+        <v>26</v>
+      </c>
+      <c r="K89">
+        <v>100</v>
+      </c>
+      <c r="L89" t="b">
+        <v>1</v>
+      </c>
+      <c r="M89" t="b">
+        <v>1</v>
+      </c>
+      <c r="N89" t="b">
+        <v>1</v>
+      </c>
+      <c r="O89">
+        <v>25</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>177</v>
+      </c>
+      <c r="S89" t="b">
+        <v>1</v>
+      </c>
+      <c r="T89" t="b">
+        <v>1</v>
+      </c>
+      <c r="U89" t="s">
+        <v>167</v>
+      </c>
+      <c r="V89" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>90</v>
+      </c>
+      <c r="B90" t="s">
+        <v>100</v>
+      </c>
+      <c r="C90" t="s">
+        <v>150</v>
+      </c>
+      <c r="D90" t="s">
+        <v>175</v>
+      </c>
+      <c r="E90" t="s">
+        <v>182</v>
+      </c>
+      <c r="J90" t="s">
+        <v>26</v>
+      </c>
+      <c r="K90">
+        <v>100</v>
+      </c>
+      <c r="L90" t="b">
+        <v>1</v>
+      </c>
+      <c r="M90" t="b">
+        <v>1</v>
+      </c>
+      <c r="N90" t="b">
+        <v>1</v>
+      </c>
+      <c r="O90">
+        <v>25</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>177</v>
+      </c>
+      <c r="S90" t="b">
+        <v>1</v>
+      </c>
+      <c r="T90" t="b">
+        <v>1</v>
+      </c>
+      <c r="U90" t="s">
+        <v>167</v>
+      </c>
+      <c r="V90" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>91</v>
+      </c>
+      <c r="B91" t="s">
+        <v>183</v>
+      </c>
+      <c r="C91" t="s">
+        <v>150</v>
+      </c>
+      <c r="D91" t="s">
+        <v>175</v>
+      </c>
+      <c r="E91" t="s">
+        <v>182</v>
+      </c>
+      <c r="J91" t="s">
+        <v>26</v>
+      </c>
+      <c r="K91">
+        <v>100</v>
+      </c>
+      <c r="L91" t="b">
+        <v>1</v>
+      </c>
+      <c r="M91" t="b">
+        <v>1</v>
+      </c>
+      <c r="N91" t="b">
+        <v>1</v>
+      </c>
+      <c r="O91">
+        <v>25</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>177</v>
+      </c>
+      <c r="S91" t="b">
+        <v>1</v>
+      </c>
+      <c r="T91" t="b">
+        <v>1</v>
+      </c>
+      <c r="V91" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscarcuellar/ocn/media/apify_client/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B0D6EC-1CB1-484D-B240-0B00C83F9422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBD7FA6-8465-AF4D-8B6D-FBC8E318AD79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6680" yWindow="700" windowWidth="32860" windowHeight="26620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="185">
   <si>
     <t>task_id</t>
   </si>
@@ -585,6 +585,9 @@
   </si>
   <si>
     <t>tiktok_posts</t>
+  </si>
+  <si>
+    <t>Conserva sólo las publicaciones que hablen del evento Zona Fest en Querétaro, o temas relacionados (si menciona Zona Fest o variaciones y parece ser de México es muy probable que sí se refiera a este evento)</t>
   </si>
 </sst>
 </file>
@@ -5332,11 +5335,14 @@
       <c r="E91" t="s">
         <v>182</v>
       </c>
+      <c r="G91" t="s">
+        <v>21</v>
+      </c>
       <c r="J91" t="s">
-        <v>26</v>
+        <v>178</v>
       </c>
       <c r="K91">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L91" t="b">
         <v>1</v>
@@ -5351,7 +5357,7 @@
         <v>25</v>
       </c>
       <c r="Q91" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="S91" t="b">
         <v>1</v>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscarcuellar/ocn/media/apify_client/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBD7FA6-8465-AF4D-8B6D-FBC8E318AD79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FBADE3-A3FA-BB48-A7CE-385C8542ECF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6680" yWindow="700" windowWidth="32860" windowHeight="26620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="31920" windowHeight="20780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tasks" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="203">
   <si>
     <t>task_id</t>
   </si>
@@ -588,13 +588,67 @@
   </si>
   <si>
     <t>Conserva sólo las publicaciones que hablen del evento Zona Fest en Querétaro, o temas relacionados (si menciona Zona Fest o variaciones y parece ser de México es muy probable que sí se refiera a este evento)</t>
+  </si>
+  <si>
+    <t>{"timeframe":"1d","enrich":true, "topics": "BUSINESS"}</t>
+  </si>
+  <si>
+    <t>Business News</t>
+  </si>
+  <si>
+    <t>top_news</t>
+  </si>
+  <si>
+    <t>World News</t>
+  </si>
+  <si>
+    <t>{"timeframe":"1d","enrich":true, "topics": "WORLD"}</t>
+  </si>
+  <si>
+    <t>{"timeframe":"1d","enrich":true, "topics": "NATION"}</t>
+  </si>
+  <si>
+    <t>Nation News</t>
+  </si>
+  <si>
+    <t>Technology News</t>
+  </si>
+  <si>
+    <t>{"timeframe":"1d","enrich":true, "topics": "TECHNOLOGY"}</t>
+  </si>
+  <si>
+    <t>{"get_comments_after_likes": 34, "enrich_author_after_likes": 100}</t>
+  </si>
+  <si>
+    <t>chepe_guerrero</t>
+  </si>
+  <si>
+    <t>Chepe Guerrero Search</t>
+  </si>
+  <si>
+    <t>chepe guerrero</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/ChepeGro/</t>
+  </si>
+  <si>
+    <t>David Guerrero Corregidora</t>
+  </si>
+  <si>
+    <t>Chepe Guerrero FB</t>
+  </si>
+  <si>
+    <t>David Guerrero Search</t>
+  </si>
+  <si>
+    <t>Conserva sólo las publicaciones que mencionen o hablen del alcalde de corregidora, Chepe Guerrero (Josué David Guerrero)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -606,6 +660,13 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -632,9 +693,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -970,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V91"/>
+  <dimension ref="A1:V98"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="19.6640625" customWidth="1"/>
@@ -4951,12 +5013,12 @@
         <v>30</v>
       </c>
       <c r="C83" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="D83" t="s">
         <v>166</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E83" s="1" t="s">
         <v>165</v>
       </c>
       <c r="F83">
@@ -4966,7 +5028,7 @@
         <v>26</v>
       </c>
       <c r="K83">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="L83" t="b">
         <v>1</v>
@@ -5042,7 +5104,7 @@
         <v>100</v>
       </c>
       <c r="C85" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="D85" t="s">
         <v>170</v>
@@ -5066,7 +5128,7 @@
         <v>1</v>
       </c>
       <c r="O85">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="Q85" t="s">
         <v>171</v>
@@ -5078,7 +5140,10 @@
         <v>1</v>
       </c>
       <c r="U85" t="s">
-        <v>167</v>
+        <v>194</v>
+      </c>
+      <c r="V85" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.2">
@@ -5366,6 +5431,317 @@
         <v>1</v>
       </c>
       <c r="V91" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>92</v>
+      </c>
+      <c r="B92" t="s">
+        <v>19</v>
+      </c>
+      <c r="C92" t="s">
+        <v>187</v>
+      </c>
+      <c r="D92" t="s">
+        <v>186</v>
+      </c>
+      <c r="G92" t="s">
+        <v>21</v>
+      </c>
+      <c r="H92" t="s">
+        <v>22</v>
+      </c>
+      <c r="J92" t="s">
+        <v>23</v>
+      </c>
+      <c r="K92">
+        <v>10</v>
+      </c>
+      <c r="L92" t="b">
+        <v>1</v>
+      </c>
+      <c r="M92" t="b">
+        <v>1</v>
+      </c>
+      <c r="N92" t="b">
+        <v>0</v>
+      </c>
+      <c r="U92" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>93</v>
+      </c>
+      <c r="B93" t="s">
+        <v>19</v>
+      </c>
+      <c r="C93" t="s">
+        <v>187</v>
+      </c>
+      <c r="D93" t="s">
+        <v>188</v>
+      </c>
+      <c r="G93" t="s">
+        <v>21</v>
+      </c>
+      <c r="H93" t="s">
+        <v>22</v>
+      </c>
+      <c r="J93" t="s">
+        <v>23</v>
+      </c>
+      <c r="K93">
+        <v>10</v>
+      </c>
+      <c r="L93" t="b">
+        <v>1</v>
+      </c>
+      <c r="M93" t="b">
+        <v>1</v>
+      </c>
+      <c r="N93" t="b">
+        <v>0</v>
+      </c>
+      <c r="U93" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>94</v>
+      </c>
+      <c r="B94" t="s">
+        <v>19</v>
+      </c>
+      <c r="C94" t="s">
+        <v>187</v>
+      </c>
+      <c r="D94" t="s">
+        <v>191</v>
+      </c>
+      <c r="G94" t="s">
+        <v>21</v>
+      </c>
+      <c r="H94" t="s">
+        <v>22</v>
+      </c>
+      <c r="J94" t="s">
+        <v>23</v>
+      </c>
+      <c r="K94">
+        <v>10</v>
+      </c>
+      <c r="L94" t="b">
+        <v>1</v>
+      </c>
+      <c r="M94" t="b">
+        <v>1</v>
+      </c>
+      <c r="N94" t="b">
+        <v>0</v>
+      </c>
+      <c r="U94" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A95" s="2">
+        <v>95</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I95" s="2"/>
+      <c r="J95" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K95" s="2">
+        <v>10</v>
+      </c>
+      <c r="L95" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M95" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="N95" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O95" s="2"/>
+      <c r="P95" s="2"/>
+      <c r="Q95" s="2"/>
+      <c r="R95" s="2"/>
+      <c r="S95" s="2"/>
+      <c r="T95" s="2"/>
+      <c r="U95" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>96</v>
+      </c>
+      <c r="B96" t="s">
+        <v>100</v>
+      </c>
+      <c r="C96" t="s">
+        <v>195</v>
+      </c>
+      <c r="D96" t="s">
+        <v>196</v>
+      </c>
+      <c r="E96" t="s">
+        <v>197</v>
+      </c>
+      <c r="J96" t="s">
+        <v>26</v>
+      </c>
+      <c r="K96">
+        <v>100</v>
+      </c>
+      <c r="L96" t="b">
+        <v>1</v>
+      </c>
+      <c r="M96" t="b">
+        <v>1</v>
+      </c>
+      <c r="N96" t="b">
+        <v>1</v>
+      </c>
+      <c r="O96">
+        <v>30</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>202</v>
+      </c>
+      <c r="S96" t="b">
+        <v>1</v>
+      </c>
+      <c r="T96" t="b">
+        <v>1</v>
+      </c>
+      <c r="U96" t="s">
+        <v>194</v>
+      </c>
+      <c r="V96" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>97</v>
+      </c>
+      <c r="B97" t="s">
+        <v>30</v>
+      </c>
+      <c r="C97" t="s">
+        <v>195</v>
+      </c>
+      <c r="D97" t="s">
+        <v>200</v>
+      </c>
+      <c r="E97" t="s">
+        <v>198</v>
+      </c>
+      <c r="J97" t="s">
+        <v>26</v>
+      </c>
+      <c r="K97">
+        <v>50</v>
+      </c>
+      <c r="L97" t="b">
+        <v>1</v>
+      </c>
+      <c r="M97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N97" t="b">
+        <v>1</v>
+      </c>
+      <c r="O97">
+        <v>30</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>202</v>
+      </c>
+      <c r="S97" t="b">
+        <v>1</v>
+      </c>
+      <c r="T97" t="b">
+        <v>1</v>
+      </c>
+      <c r="U97" t="s">
+        <v>194</v>
+      </c>
+      <c r="V97" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>98</v>
+      </c>
+      <c r="B98" t="s">
+        <v>100</v>
+      </c>
+      <c r="C98" t="s">
+        <v>195</v>
+      </c>
+      <c r="D98" t="s">
+        <v>201</v>
+      </c>
+      <c r="E98" t="s">
+        <v>199</v>
+      </c>
+      <c r="J98" t="s">
+        <v>26</v>
+      </c>
+      <c r="K98">
+        <v>100</v>
+      </c>
+      <c r="L98" t="b">
+        <v>1</v>
+      </c>
+      <c r="M98" t="b">
+        <v>1</v>
+      </c>
+      <c r="N98" t="b">
+        <v>1</v>
+      </c>
+      <c r="O98">
+        <v>30</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>202</v>
+      </c>
+      <c r="S98" t="b">
+        <v>1</v>
+      </c>
+      <c r="T98" t="b">
+        <v>1</v>
+      </c>
+      <c r="U98" t="s">
+        <v>194</v>
+      </c>
+      <c r="V98" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5376,6 +5752,7 @@
     <hyperlink ref="E9" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="E18" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="E19" r:id="rId5" xr:uid="{EF120849-7F87-E243-BFC1-62D2F61B5DE4}"/>
+    <hyperlink ref="E83" r:id="rId6" xr:uid="{9F2731B3-9CAD-BF41-AA4E-892713E3BC14}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscarcuellar/ocn/media/apify_client/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FBADE3-A3FA-BB48-A7CE-385C8542ECF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F814E873-98CA-CD4A-98F0-EAD960B8A18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="31920" windowHeight="20780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="31920" windowHeight="20780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tasks" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="221">
   <si>
     <t>task_id</t>
   </si>
@@ -642,6 +642,60 @@
   </si>
   <si>
     <t>Conserva sólo las publicaciones que mencionen o hablen del alcalde de corregidora, Chepe Guerrero (Josué David Guerrero)</t>
+  </si>
+  <si>
+    <t>efren_cuevas</t>
+  </si>
+  <si>
+    <t>Efrén Cuevas</t>
+  </si>
+  <si>
+    <t>efren cuevas</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/marianardzcantu1</t>
+  </si>
+  <si>
+    <t>Mariana Rodríguez FB</t>
+  </si>
+  <si>
+    <t>mc</t>
+  </si>
+  <si>
+    <t>Conserva sólo las publicaciones que mencionen o hablen de Mariana Rodríguez, esposa del gobernador de Nuevo León, Samuel García y precandidata a la gubernatura de ese estado.</t>
+  </si>
+  <si>
+    <t>{"get_comments_after_likes": 50, "enrich_author_after_likes": 100}</t>
+  </si>
+  <si>
+    <t>Mariana Rodríguez</t>
+  </si>
+  <si>
+    <t>Colosio FB</t>
+  </si>
+  <si>
+    <t>Colosio</t>
+  </si>
+  <si>
+    <t>Luis Donaldo Colosio</t>
+  </si>
+  <si>
+    <t>Conserva sólo las publicaciones que mencionen o hablen de Luis Donaldo Colosio Riojas, quien es un político mexicano, miembro del partido Movimiento Ciudadano. Actualmente es senador de la República y precandidato a la gobernatura de Sonora.</t>
+  </si>
+  <si>
+    <t>Javier Lamarque FB</t>
+  </si>
+  <si>
+    <t>Javier Lamarque</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/javierlamarquecano</t>
+  </si>
+  <si>
+    <t>Conserva sólo las publicaciones que mencionen o hablen de Javier Lamarque. Presidente Municipal de Cajeme 2024-2027, Sonora y precandidato a la gobernatura de Sonora.</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/colosioriojas</t>
   </si>
 </sst>
 </file>
@@ -1032,7 +1086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V98"/>
+  <dimension ref="A1:V105"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="19.6640625" customWidth="1"/>
@@ -5679,9 +5733,6 @@
       <c r="O97">
         <v>30</v>
       </c>
-      <c r="Q97" t="s">
-        <v>202</v>
-      </c>
       <c r="S97" t="b">
         <v>1</v>
       </c>
@@ -5742,6 +5793,359 @@
         <v>194</v>
       </c>
       <c r="V98" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>99</v>
+      </c>
+      <c r="B99" t="s">
+        <v>100</v>
+      </c>
+      <c r="C99" t="s">
+        <v>203</v>
+      </c>
+      <c r="D99" t="s">
+        <v>204</v>
+      </c>
+      <c r="E99" t="s">
+        <v>205</v>
+      </c>
+      <c r="G99" t="s">
+        <v>21</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J99" t="s">
+        <v>26</v>
+      </c>
+      <c r="K99">
+        <v>150</v>
+      </c>
+      <c r="L99" t="b">
+        <v>1</v>
+      </c>
+      <c r="M99" t="b">
+        <v>1</v>
+      </c>
+      <c r="N99" t="b">
+        <v>0</v>
+      </c>
+      <c r="O99">
+        <v>25</v>
+      </c>
+      <c r="S99" t="b">
+        <v>1</v>
+      </c>
+      <c r="T99" t="b">
+        <v>1</v>
+      </c>
+      <c r="U99" t="s">
+        <v>167</v>
+      </c>
+      <c r="V99" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>100</v>
+      </c>
+      <c r="B100" t="s">
+        <v>30</v>
+      </c>
+      <c r="C100" t="s">
+        <v>208</v>
+      </c>
+      <c r="D100" t="s">
+        <v>207</v>
+      </c>
+      <c r="E100" t="s">
+        <v>206</v>
+      </c>
+      <c r="G100" t="s">
+        <v>21</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J100" t="s">
+        <v>26</v>
+      </c>
+      <c r="K100">
+        <v>150</v>
+      </c>
+      <c r="L100" t="b">
+        <v>1</v>
+      </c>
+      <c r="M100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N100" t="b">
+        <v>1</v>
+      </c>
+      <c r="O100">
+        <v>25</v>
+      </c>
+      <c r="V100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>101</v>
+      </c>
+      <c r="B101" t="s">
+        <v>100</v>
+      </c>
+      <c r="C101" t="s">
+        <v>208</v>
+      </c>
+      <c r="D101" t="s">
+        <v>211</v>
+      </c>
+      <c r="E101" t="s">
+        <v>211</v>
+      </c>
+      <c r="G101" t="s">
+        <v>21</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J101" t="s">
+        <v>26</v>
+      </c>
+      <c r="K101">
+        <v>150</v>
+      </c>
+      <c r="L101" t="b">
+        <v>1</v>
+      </c>
+      <c r="M101" t="b">
+        <v>1</v>
+      </c>
+      <c r="N101" t="b">
+        <v>1</v>
+      </c>
+      <c r="O101">
+        <v>25</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>209</v>
+      </c>
+      <c r="S101" t="b">
+        <v>1</v>
+      </c>
+      <c r="T101" t="b">
+        <v>1</v>
+      </c>
+      <c r="U101" t="s">
+        <v>210</v>
+      </c>
+      <c r="V101" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>102</v>
+      </c>
+      <c r="B102" t="s">
+        <v>30</v>
+      </c>
+      <c r="C102" t="s">
+        <v>208</v>
+      </c>
+      <c r="D102" t="s">
+        <v>212</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G102" t="s">
+        <v>21</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J102" t="s">
+        <v>26</v>
+      </c>
+      <c r="K102">
+        <v>150</v>
+      </c>
+      <c r="L102" t="b">
+        <v>1</v>
+      </c>
+      <c r="M102" t="b">
+        <v>1</v>
+      </c>
+      <c r="N102" t="b">
+        <v>1</v>
+      </c>
+      <c r="O102">
+        <v>25</v>
+      </c>
+      <c r="V102" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>103</v>
+      </c>
+      <c r="B103" t="s">
+        <v>100</v>
+      </c>
+      <c r="C103" t="s">
+        <v>208</v>
+      </c>
+      <c r="D103" t="s">
+        <v>213</v>
+      </c>
+      <c r="E103" t="s">
+        <v>214</v>
+      </c>
+      <c r="G103" t="s">
+        <v>21</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J103" t="s">
+        <v>26</v>
+      </c>
+      <c r="K103">
+        <v>150</v>
+      </c>
+      <c r="L103" t="b">
+        <v>1</v>
+      </c>
+      <c r="M103" t="b">
+        <v>1</v>
+      </c>
+      <c r="N103" t="b">
+        <v>1</v>
+      </c>
+      <c r="O103">
+        <v>25</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>215</v>
+      </c>
+      <c r="S103" t="b">
+        <v>1</v>
+      </c>
+      <c r="T103" t="b">
+        <v>1</v>
+      </c>
+      <c r="U103" t="s">
+        <v>210</v>
+      </c>
+      <c r="V103" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>104</v>
+      </c>
+      <c r="B104" t="s">
+        <v>30</v>
+      </c>
+      <c r="C104" t="s">
+        <v>208</v>
+      </c>
+      <c r="D104" t="s">
+        <v>216</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G104" t="s">
+        <v>21</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J104" t="s">
+        <v>26</v>
+      </c>
+      <c r="K104">
+        <v>150</v>
+      </c>
+      <c r="L104" t="b">
+        <v>1</v>
+      </c>
+      <c r="M104" t="b">
+        <v>1</v>
+      </c>
+      <c r="N104" t="b">
+        <v>1</v>
+      </c>
+      <c r="O104">
+        <v>25</v>
+      </c>
+      <c r="V104" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>105</v>
+      </c>
+      <c r="B105" t="s">
+        <v>100</v>
+      </c>
+      <c r="C105" t="s">
+        <v>208</v>
+      </c>
+      <c r="D105" t="s">
+        <v>217</v>
+      </c>
+      <c r="E105" t="s">
+        <v>217</v>
+      </c>
+      <c r="G105" t="s">
+        <v>21</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J105" t="s">
+        <v>26</v>
+      </c>
+      <c r="K105">
+        <v>150</v>
+      </c>
+      <c r="L105" t="b">
+        <v>1</v>
+      </c>
+      <c r="M105" t="b">
+        <v>1</v>
+      </c>
+      <c r="N105" t="b">
+        <v>1</v>
+      </c>
+      <c r="O105">
+        <v>25</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>219</v>
+      </c>
+      <c r="S105" t="b">
+        <v>1</v>
+      </c>
+      <c r="T105" t="b">
+        <v>1</v>
+      </c>
+      <c r="U105" t="s">
+        <v>210</v>
+      </c>
+      <c r="V105" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5753,6 +6157,8 @@
     <hyperlink ref="E18" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="E19" r:id="rId5" xr:uid="{EF120849-7F87-E243-BFC1-62D2F61B5DE4}"/>
     <hyperlink ref="E83" r:id="rId6" xr:uid="{9F2731B3-9CAD-BF41-AA4E-892713E3BC14}"/>
+    <hyperlink ref="E104" r:id="rId7" xr:uid="{E1349C62-4C49-1C43-AD91-9617B3411341}"/>
+    <hyperlink ref="E102" r:id="rId8" xr:uid="{F4B54EF3-95F7-1B46-912A-493D572CF022}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
